--- a/outputs/EH2_stc_results_2026-05-20.xlsx
+++ b/outputs/EH2_stc_results_2026-05-20.xlsx
@@ -637,19 +637,19 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>55.82429854096524</v>
+        <v>55.754917865524</v>
       </c>
       <c r="L3" t="n">
         <v>69.95</v>
       </c>
       <c r="M3" t="n">
-        <v>41.87429854096523</v>
+        <v>41.804917865524</v>
       </c>
       <c r="N3" t="n">
         <v>3.552713678800501e-15</v>
       </c>
       <c r="O3" t="n">
-        <v>161.4555555555556</v>
+        <v>161.3868686868688</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -714,7 +714,7 @@
         <v>16.61100000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>144.6767676767677</v>
+        <v>144.6080808080808</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -746,7 +746,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>68.551</v>
+        <v>68.483</v>
       </c>
       <c r="E5" t="n">
         <v>38.078</v>
@@ -773,10 +773,10 @@
         <v>54.5</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.794299837778031e-14</v>
+        <v>-3.229739708000455e-14</v>
       </c>
       <c r="N5" t="n">
-        <v>15.141</v>
+        <v>15.073</v>
       </c>
       <c r="O5" t="n">
         <v>129.3828282828283</v>
@@ -941,7 +941,7 @@
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>75.066</v>
+        <v>84.11799999999999</v>
       </c>
       <c r="E8" t="n">
         <v>48.821</v>
@@ -962,19 +962,19 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>150.7598814365048</v>
+        <v>172.8065334857542</v>
       </c>
       <c r="L8" t="n">
-        <v>76.59795918367347</v>
+        <v>85.834693877551</v>
       </c>
       <c r="M8" t="n">
-        <v>153.1619222528313</v>
+        <v>165.9718396082032</v>
       </c>
       <c r="N8" t="n">
-        <v>-7.105427357601002e-15</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="O8" t="n">
-        <v>271.630303030303</v>
+        <v>284.3121212121212</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1039,7 +1039,7 @@
         <v>15.51799999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>255.9555555555555</v>
+        <v>268.6373737373737</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1104,7 +1104,7 @@
         <v>61.17299999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>194.1646464646465</v>
+        <v>206.8464646464647</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1136,7 +1136,7 @@
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>125.853</v>
+        <v>138.408</v>
       </c>
       <c r="E11" t="n">
         <v>45.383</v>
@@ -1166,7 +1166,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>73.42299999999997</v>
+        <v>85.97799999999998</v>
       </c>
       <c r="O11" t="n">
         <v>120</v>
@@ -1219,7 +1219,7 @@
         <v>34</v>
       </c>
       <c r="J12" t="n">
-        <v>275.144090669632</v>
+        <v>281.1437845784168</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1228,13 +1228,13 @@
         <v>141.2326530612245</v>
       </c>
       <c r="M12" t="n">
-        <v>133.9114376084074</v>
+        <v>139.9111315171922</v>
       </c>
       <c r="N12" t="n">
         <v>7.105427357601002e-15</v>
       </c>
       <c r="O12" t="n">
-        <v>252.5723232323233</v>
+        <v>258.5120202020203</v>
       </c>
       <c r="P12" t="n">
         <v>1</v>
@@ -1290,7 +1290,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>34</v>
+        <v>34.00000000000003</v>
       </c>
       <c r="M13" t="n">
         <v>1.435439870222425e-14</v>
@@ -1299,7 +1299,7 @@
         <v>105.767</v>
       </c>
       <c r="O13" t="n">
-        <v>145.7369696969698</v>
+        <v>151.6766666666668</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1331,7 +1331,7 @@
         <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>139.087</v>
+        <v>136.236</v>
       </c>
       <c r="E14" t="n">
         <v>56.911</v>
@@ -1343,19 +1343,19 @@
         <v>35</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4797979797979224</v>
+        <v>0.4797979797979792</v>
       </c>
       <c r="I14" t="n">
-        <v>34.52020202020208</v>
+        <v>34.52020202020202</v>
       </c>
       <c r="J14" t="n">
-        <v>142.4457122242837</v>
+        <v>139.5365285508143</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>141.9255102040816</v>
+        <v>139.0163265306122</v>
       </c>
       <c r="M14" t="n">
         <v>0.9999999999999949</v>
@@ -1364,7 +1364,7 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>146.7269696969698</v>
+        <v>152.6666666666668</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
@@ -1408,10 +1408,10 @@
         <v>54.5</v>
       </c>
       <c r="H15" t="n">
-        <v>3.5</v>
+        <v>3.499999999999972</v>
       </c>
       <c r="I15" t="n">
-        <v>51</v>
+        <v>51.00000000000003</v>
       </c>
       <c r="J15" t="n">
         <v>134.4959183673469</v>
@@ -1429,7 +1429,7 @@
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>145.7168686868688</v>
+        <v>151.6565656565657</v>
       </c>
       <c r="P15" t="n">
         <v>-0</v>
@@ -1479,25 +1479,25 @@
         <v>107</v>
       </c>
       <c r="J16" t="n">
-        <v>124.284693877551</v>
+        <v>253.9616718512663</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>124.284693877551</v>
+        <v>125.3051020408163</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>128.65656981045</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>144.7067676767678</v>
+        <v>279.0265697689113</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" t="n">
         <v>59.53444444444445</v>
@@ -1526,7 +1526,7 @@
         <v>16</v>
       </c>
       <c r="D17" t="n">
-        <v>122.799</v>
+        <v>140.444</v>
       </c>
       <c r="E17" t="n">
         <v>41.57</v>
@@ -1544,22 +1544,22 @@
         <v>163</v>
       </c>
       <c r="J17" t="n">
-        <v>698.3102040816327</v>
+        <v>703.3102040816327</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>125.3051020408163</v>
+        <v>143.3102040816326</v>
       </c>
       <c r="M17" t="n">
-        <v>573.0051020408163</v>
+        <v>560</v>
       </c>
       <c r="N17" t="n">
         <v>-7.105427357601002e-15</v>
       </c>
       <c r="O17" t="n">
-        <v>711.9818186971759</v>
+        <v>833.4265697689112</v>
       </c>
       <c r="P17" t="n">
         <v>1</v>
@@ -1603,31 +1603,31 @@
         <v>219.5</v>
       </c>
       <c r="H18" t="n">
-        <v>54.010100478967</v>
+        <v>38.5000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>165.489899521033</v>
+        <v>180.9999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>90.3001036026656</v>
+        <v>103.7897959183673</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>143.3102040816326</v>
+        <v>142.2897959183673</v>
       </c>
       <c r="M18" t="n">
-        <v>1.000000000000031</v>
+        <v>7.894919286223335e-14</v>
       </c>
       <c r="N18" t="n">
-        <v>-7.105427357601002e-15</v>
+        <v>0.9999999999999929</v>
       </c>
       <c r="O18" t="n">
-        <v>712.9718186971759</v>
+        <v>832.4164687588103</v>
       </c>
       <c r="P18" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="Q18" t="n">
         <v>46.18888888888889</v>
@@ -1668,13 +1668,13 @@
         <v>285.5</v>
       </c>
       <c r="H19" t="n">
-        <v>57.49999999999999</v>
+        <v>42.47969594939298</v>
       </c>
       <c r="I19" t="n">
-        <v>228</v>
+        <v>243.020304050607</v>
       </c>
       <c r="J19" t="n">
-        <v>68.80918367346938</v>
+        <v>83.82948772407644</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1689,7 +1689,7 @@
         <v>7.105427357601002e-15</v>
       </c>
       <c r="O19" t="n">
-        <v>713.9618186971759</v>
+        <v>833.4064687588103</v>
       </c>
       <c r="P19" t="n">
         <v>1</v>
@@ -1721,7 +1721,7 @@
         <v>19</v>
       </c>
       <c r="D20" t="n">
-        <v>122.803</v>
+        <v>117.645</v>
       </c>
       <c r="E20" t="n">
         <v>43.091</v>
@@ -1733,10 +1733,10 @@
         <v>320</v>
       </c>
       <c r="H20" t="n">
-        <v>126.3091836734694</v>
+        <v>121.0459183673469</v>
       </c>
       <c r="I20" t="n">
-        <v>193.6908163265306</v>
+        <v>198.9540816326531</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1745,7 +1745,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>125.3091836734694</v>
+        <v>120.0459183673469</v>
       </c>
       <c r="M20" t="n">
         <v>1.000000000000016</v>
@@ -1754,7 +1754,7 @@
         <v>7.105427357601002e-15</v>
       </c>
       <c r="O20" t="n">
-        <v>714.9518186971759</v>
+        <v>834.3964687588103</v>
       </c>
       <c r="P20" t="n">
         <v>1</v>
@@ -1819,7 +1819,7 @@
         <v>7.105427357601002e-15</v>
       </c>
       <c r="O21" t="n">
-        <v>715.9418186971759</v>
+        <v>835.3864687588103</v>
       </c>
       <c r="P21" t="n">
         <v>1</v>
@@ -1863,10 +1863,10 @@
         <v>296</v>
       </c>
       <c r="H22" t="n">
-        <v>121.3102040816327</v>
+        <v>123.330612244898</v>
       </c>
       <c r="I22" t="n">
-        <v>174.6897959183673</v>
+        <v>172.669387755102</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1875,19 +1875,19 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>121.3102040816327</v>
+        <v>122.330612244898</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>0.9999999999999929</v>
+        <v>-7.105427357601002e-15</v>
       </c>
       <c r="O22" t="n">
-        <v>714.9317176870749</v>
+        <v>836.3764687588103</v>
       </c>
       <c r="P22" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="Q22" t="n">
         <v>49.58333333333333</v>
@@ -1916,7 +1916,7 @@
         <v>22</v>
       </c>
       <c r="D23" t="n">
-        <v>119.884</v>
+        <v>110.043</v>
       </c>
       <c r="E23" t="n">
         <v>40.775</v>
@@ -1928,10 +1928,10 @@
         <v>280</v>
       </c>
       <c r="H23" t="n">
-        <v>121.3102040816327</v>
+        <v>111.2683673469388</v>
       </c>
       <c r="I23" t="n">
-        <v>158.6897959183673</v>
+        <v>168.7316326530612</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1940,16 +1940,16 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>121.3102040816327</v>
+        <v>111.2683673469388</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1.4210854715202e-14</v>
       </c>
       <c r="N23" t="n">
         <v>0.9999999999999929</v>
       </c>
       <c r="O23" t="n">
-        <v>713.9216166769738</v>
+        <v>835.3663677487093</v>
       </c>
       <c r="P23" t="n">
         <v>-0</v>
@@ -1993,10 +1993,10 @@
         <v>270.5</v>
       </c>
       <c r="H24" t="n">
-        <v>243.4864313095915</v>
+        <v>120.8149655805658</v>
       </c>
       <c r="I24" t="n">
-        <v>27.0135686904085</v>
+        <v>149.6850344194343</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2008,7 +2008,7 @@
         <v>112.2887755102041</v>
       </c>
       <c r="M24" t="n">
-        <v>131.1976557993874</v>
+        <v>8.52619007036165</v>
       </c>
       <c r="N24" t="n">
         <v>7.105427357601002e-15</v>
@@ -2306,7 +2306,7 @@
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>68.551</v>
+        <v>68.483</v>
       </c>
       <c r="E29" t="n">
         <v>38.078</v>
@@ -2327,13 +2327,13 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>64.45</v>
+        <v>64.38061224489795</v>
       </c>
       <c r="L29" t="n">
-        <v>69.95</v>
+        <v>69.88061224489796</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0.9999999999999858</v>
       </c>
       <c r="N29" t="n">
         <v>-3.552713678800501e-15</v>
@@ -2392,19 +2392,19 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>500.7092521795985</v>
+        <v>522.7549618010657</v>
       </c>
       <c r="L30" t="n">
         <v>69.88061224489796</v>
       </c>
       <c r="M30" t="n">
-        <v>438.3286399347006</v>
+        <v>460.3743495561678</v>
       </c>
       <c r="N30" t="n">
         <v>-3.552713678800501e-15</v>
       </c>
       <c r="O30" t="n">
-        <v>554.9353535353536</v>
+        <v>576.7606060606061</v>
       </c>
       <c r="P30" t="n">
         <v>1</v>
@@ -2469,7 +2469,7 @@
         <v>65.756</v>
       </c>
       <c r="O31" t="n">
-        <v>488.5151515151515</v>
+        <v>510.340404040404</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -2501,7 +2501,7 @@
         <v>7</v>
       </c>
       <c r="D32" t="n">
-        <v>75.066</v>
+        <v>84.11799999999999</v>
       </c>
       <c r="E32" t="n">
         <v>48.821</v>
@@ -2531,10 +2531,10 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>61.836</v>
+        <v>70.88799999999999</v>
       </c>
       <c r="O32" t="n">
-        <v>426.0545454545455</v>
+        <v>438.7363636363636</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         <v>68.92799999999998</v>
       </c>
       <c r="O33" t="n">
-        <v>356.430303030303</v>
+        <v>369.1121212121212</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -2658,13 +2658,13 @@
         <v>12.5</v>
       </c>
       <c r="M34" t="n">
-        <v>-3.588599675556062e-15</v>
+        <v>2.512019772889244e-14</v>
       </c>
       <c r="N34" t="n">
         <v>113.603</v>
       </c>
       <c r="O34" t="n">
-        <v>241.679797979798</v>
+        <v>254.3616161616162</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -2696,7 +2696,7 @@
         <v>10</v>
       </c>
       <c r="D35" t="n">
-        <v>125.853</v>
+        <v>138.408</v>
       </c>
       <c r="E35" t="n">
         <v>45.383</v>
@@ -2723,10 +2723,10 @@
         <v>5.5</v>
       </c>
       <c r="M35" t="n">
-        <v>-8.971499188890156e-15</v>
+        <v>1.973729821555834e-14</v>
       </c>
       <c r="N35" t="n">
-        <v>120.463</v>
+        <v>133.018</v>
       </c>
       <c r="O35" t="n">
         <v>120</v>
@@ -2779,7 +2779,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>275.144090669632</v>
+        <v>281.1437845784168</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -2788,13 +2788,13 @@
         <v>141.2326530612245</v>
       </c>
       <c r="M36" t="n">
-        <v>137.9114376084074</v>
+        <v>143.9111315171922</v>
       </c>
       <c r="N36" t="n">
         <v>7.105427357601002e-15</v>
       </c>
       <c r="O36" t="n">
-        <v>256.5323232323233</v>
+        <v>262.4720202020203</v>
       </c>
       <c r="P36" t="n">
         <v>1</v>
@@ -2850,19 +2850,19 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>4.000000000000004</v>
+        <v>4</v>
       </c>
       <c r="M37" t="n">
-        <v>-3.364312195833807e-14</v>
+        <v>2.736307252611497e-14</v>
       </c>
       <c r="N37" t="n">
         <v>135.167</v>
       </c>
       <c r="O37" t="n">
-        <v>120</v>
+        <v>125.9396969696971</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q37" t="n">
         <v>55</v>
@@ -2891,7 +2891,7 @@
         <v>13</v>
       </c>
       <c r="D38" t="n">
-        <v>139.087</v>
+        <v>136.236</v>
       </c>
       <c r="E38" t="n">
         <v>56.911</v>
@@ -2909,22 +2909,22 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>142.4457122242837</v>
+        <v>139.5365285508143</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>141.9255102040816</v>
+        <v>139.0163265306122</v>
       </c>
       <c r="M38" t="n">
-        <v>4.520202020202029</v>
+        <v>4.520202020202</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>124.475</v>
+        <v>130.4146969696971</v>
       </c>
       <c r="P38" t="n">
         <v>1</v>
@@ -2989,7 +2989,7 @@
         <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>123.464898989899</v>
+        <v>129.404595959596</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -3039,7 +3039,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>124.284693877551</v>
+        <v>253.9616718512663</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -3048,13 +3048,13 @@
         <v>125.3051020408163</v>
       </c>
       <c r="M40" t="n">
-        <v>7.979591836734693</v>
+        <v>137.6565698104501</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>131.3646949082663</v>
+        <v>265.6846000719416</v>
       </c>
       <c r="P40" t="n">
         <v>1</v>
@@ -3086,7 +3086,7 @@
         <v>16</v>
       </c>
       <c r="D41" t="n">
-        <v>122.799</v>
+        <v>140.444</v>
       </c>
       <c r="E41" t="n">
         <v>41.57</v>
@@ -3104,22 +3104,22 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>698.3102040816327</v>
+        <v>703.3102040816327</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>125.3051020408163</v>
+        <v>143.3102040816326</v>
       </c>
       <c r="M41" t="n">
-        <v>584.0051020408164</v>
+        <v>571</v>
       </c>
       <c r="N41" t="n">
         <v>-7.105427357601002e-15</v>
       </c>
       <c r="O41" t="n">
-        <v>709.5297459286745</v>
+        <v>830.9746000719416</v>
       </c>
       <c r="P41" t="n">
         <v>1</v>
@@ -3169,25 +3169,25 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>90.3001036026656</v>
+        <v>103.7897959183673</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>101.3001036026656</v>
+        <v>114.7897959183674</v>
       </c>
       <c r="M42" t="n">
-        <v>-5.024039545778486e-14</v>
+        <v>-1.220123889689061e-13</v>
       </c>
       <c r="N42" t="n">
-        <v>41.1698984693877</v>
+        <v>27.94999999999997</v>
       </c>
       <c r="O42" t="n">
-        <v>667.9439898989899</v>
+        <v>802.7422768396183</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>-1.4210854715202e-16</v>
       </c>
       <c r="Q42" t="n">
         <v>46.18888888888889</v>
@@ -3234,22 +3234,22 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>68.80918367346938</v>
+        <v>83.82948772407644</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>89.30918367346938</v>
+        <v>104.3294877240766</v>
       </c>
       <c r="M43" t="n">
-        <v>1.291895883200182e-13</v>
+        <v>8.612639221334548e-14</v>
       </c>
       <c r="N43" t="n">
-        <v>35.28000000000001</v>
+        <v>20.56010203040497</v>
       </c>
       <c r="O43" t="n">
-        <v>632.3076262626264</v>
+        <v>781.9744970109265</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
@@ -3281,7 +3281,7 @@
         <v>19</v>
       </c>
       <c r="D44" t="n">
-        <v>122.803</v>
+        <v>117.645</v>
       </c>
       <c r="E44" t="n">
         <v>43.091</v>
@@ -3308,16 +3308,16 @@
         <v>28</v>
       </c>
       <c r="M44" t="n">
-        <v>2.512019772889243e-14</v>
+        <v>-2.655563759911486e-13</v>
       </c>
       <c r="N44" t="n">
-        <v>95.36300000000003</v>
+        <v>90.205</v>
       </c>
       <c r="O44" t="n">
-        <v>535.9813636363638</v>
+        <v>690.8583353947646</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>-3.493501784153826e-16</v>
       </c>
       <c r="Q44" t="n">
         <v>47.87888888888889</v>
@@ -3370,19 +3370,19 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>34.50000000000003</v>
+        <v>34.5</v>
       </c>
       <c r="M45" t="n">
-        <v>-2.153159805333638e-14</v>
+        <v>-5.024039545778486e-14</v>
       </c>
       <c r="N45" t="n">
-        <v>83.83499999999998</v>
+        <v>83.83500000000001</v>
       </c>
       <c r="O45" t="n">
-        <v>451.2995454545456</v>
+        <v>606.1765172129464</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q45" t="n">
         <v>47.87888888888889</v>
@@ -3444,10 +3444,10 @@
         <v>79.214</v>
       </c>
       <c r="O46" t="n">
-        <v>371.2854040404042</v>
+        <v>526.1623757988049</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q46" t="n">
         <v>49.58333333333333</v>
@@ -3476,7 +3476,7 @@
         <v>22</v>
       </c>
       <c r="D47" t="n">
-        <v>119.884</v>
+        <v>110.043</v>
       </c>
       <c r="E47" t="n">
         <v>40.775</v>
@@ -3500,19 +3500,19 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>44.50000000000001</v>
+        <v>44.5</v>
       </c>
       <c r="M47" t="n">
-        <v>-7.105427357601002e-15</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>76.274</v>
+        <v>66.43300000000002</v>
       </c>
       <c r="O47" t="n">
-        <v>294.2409595959597</v>
+        <v>459.0583353947644</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q47" t="n">
         <v>45.30555555555555</v>
@@ -3574,7 +3574,7 @@
         <v>68.88300000000004</v>
       </c>
       <c r="O48" t="n">
-        <v>224.6621717171718</v>
+        <v>389.4795475159765</v>
       </c>
       <c r="P48" t="n">
         <v>-0</v>
@@ -3630,19 +3630,19 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>33.99999999999999</v>
+        <v>34</v>
       </c>
       <c r="M49" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
         <v>68.82499999999999</v>
       </c>
       <c r="O49" t="n">
-        <v>155.1419696969697</v>
+        <v>319.9593454957745</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q49" t="n">
         <v>38.49777777777778</v>
@@ -3866,7 +3866,7 @@
         <v>4</v>
       </c>
       <c r="D53" t="n">
-        <v>68.551</v>
+        <v>68.483</v>
       </c>
       <c r="E53" t="n">
         <v>38.078</v>
@@ -3878,10 +3878,10 @@
         <v>127.5</v>
       </c>
       <c r="H53" t="n">
-        <v>98.19054448837997</v>
+        <v>120.1678087825274</v>
       </c>
       <c r="I53" t="n">
-        <v>29.30945551162003</v>
+        <v>7.332191217472612</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -3890,16 +3890,16 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>69.95</v>
+        <v>69.88061224489796</v>
       </c>
       <c r="M53" t="n">
-        <v>28.24054448837997</v>
+        <v>50.28719653762943</v>
       </c>
       <c r="N53" t="n">
         <v>-3.552713678800501e-15</v>
       </c>
       <c r="O53" t="n">
-        <v>149.9381390434962</v>
+        <v>171.7643245722531</v>
       </c>
       <c r="P53" t="n">
         <v>1</v>
@@ -3964,7 +3964,7 @@
         <v>-3.552713678800501e-15</v>
       </c>
       <c r="O54" t="n">
-        <v>200.5463329210472</v>
+        <v>222.3725184498041</v>
       </c>
       <c r="P54" t="n">
         <v>1</v>
@@ -4029,7 +4029,7 @@
         <v>-3.552713678800501e-15</v>
       </c>
       <c r="O55" t="n">
-        <v>232.6243533292104</v>
+        <v>254.4505388579674</v>
       </c>
       <c r="P55" t="n">
         <v>1</v>
@@ -4061,7 +4061,7 @@
         <v>7</v>
       </c>
       <c r="D56" t="n">
-        <v>75.066</v>
+        <v>84.11799999999999</v>
       </c>
       <c r="E56" t="n">
         <v>48.821</v>
@@ -4085,16 +4085,16 @@
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>76.59795918367347</v>
+        <v>85.834693877551</v>
       </c>
       <c r="M56" t="n">
-        <v>18.90204081632653</v>
+        <v>9.665306122448996</v>
       </c>
       <c r="N56" t="n">
-        <v>-7.105427357601002e-15</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="O56" t="n">
-        <v>251.3373737373737</v>
+        <v>264.0191919191919</v>
       </c>
       <c r="P56" t="n">
         <v>1</v>
@@ -4159,7 +4159,7 @@
         <v>3.267999999999994</v>
       </c>
       <c r="O57" t="n">
-        <v>248.0363636363636</v>
+        <v>260.7181818181818</v>
       </c>
       <c r="P57" t="n">
         <v>0</v>
@@ -4224,7 +4224,7 @@
         <v>50.39299999999999</v>
       </c>
       <c r="O58" t="n">
-        <v>197.1343434343434</v>
+        <v>209.8161616161616</v>
       </c>
       <c r="P58" t="n">
         <v>0</v>
@@ -4256,7 +4256,7 @@
         <v>10</v>
       </c>
       <c r="D59" t="n">
-        <v>125.853</v>
+        <v>138.408</v>
       </c>
       <c r="E59" t="n">
         <v>45.383</v>
@@ -4280,13 +4280,13 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>50.5</v>
+        <v>50.49999999999997</v>
       </c>
       <c r="M59" t="n">
-        <v>7.177199351112124e-15</v>
+        <v>3.588599675556061e-14</v>
       </c>
       <c r="N59" t="n">
-        <v>76.36299999999999</v>
+        <v>88.91800000000002</v>
       </c>
       <c r="O59" t="n">
         <v>120</v>
@@ -4339,7 +4339,7 @@
         <v>32</v>
       </c>
       <c r="J60" t="n">
-        <v>275.144090669632</v>
+        <v>281.1437845784168</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -4348,13 +4348,13 @@
         <v>141.2326530612245</v>
       </c>
       <c r="M60" t="n">
-        <v>133.9114376084074</v>
+        <v>139.9111315171922</v>
       </c>
       <c r="N60" t="n">
         <v>7.105427357601002e-15</v>
       </c>
       <c r="O60" t="n">
-        <v>252.5723232323233</v>
+        <v>258.5120202020203</v>
       </c>
       <c r="P60" t="n">
         <v>1</v>
@@ -4410,16 +4410,16 @@
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>64.49999999999999</v>
+        <v>64.50000000000003</v>
       </c>
       <c r="M61" t="n">
-        <v>7.177199351112124e-15</v>
+        <v>2.153159805333637e-14</v>
       </c>
       <c r="N61" t="n">
-        <v>75.87700000000001</v>
+        <v>75.87699999999995</v>
       </c>
       <c r="O61" t="n">
-        <v>175.928888888889</v>
+        <v>181.868585858586</v>
       </c>
       <c r="P61" t="n">
         <v>0</v>
@@ -4451,7 +4451,7 @@
         <v>13</v>
       </c>
       <c r="D62" t="n">
-        <v>139.087</v>
+        <v>136.236</v>
       </c>
       <c r="E62" t="n">
         <v>56.911</v>
@@ -4463,28 +4463,28 @@
         <v>78.5</v>
       </c>
       <c r="H62" t="n">
-        <v>78.5</v>
+        <v>0.4797979797979792</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>78.02020202020202</v>
       </c>
       <c r="J62" t="n">
-        <v>142.4457122242837</v>
+        <v>139.5365285508143</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>141.9255102040816</v>
+        <v>139.0163265306122</v>
       </c>
       <c r="M62" t="n">
-        <v>79.02020202020202</v>
+        <v>0.9999999999999949</v>
       </c>
       <c r="N62" t="n">
         <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>254.158888888889</v>
+        <v>182.858585858586</v>
       </c>
       <c r="P62" t="n">
         <v>1</v>
@@ -4528,10 +4528,10 @@
         <v>72.5</v>
       </c>
       <c r="H63" t="n">
-        <v>72.5</v>
+        <v>3.499999999999972</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>69.00000000000003</v>
       </c>
       <c r="J63" t="n">
         <v>134.4959183673469</v>
@@ -4540,19 +4540,19 @@
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>139.0163265306122</v>
+        <v>137.9959183673469</v>
       </c>
       <c r="M63" t="n">
-        <v>67.97959183673466</v>
+        <v>-1.435439870222425e-14</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>321.4586848072563</v>
+        <v>181.8484848484849</v>
       </c>
       <c r="P63" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="Q63" t="n">
         <v>63.23444444444444</v>
@@ -4593,13 +4593,13 @@
         <v>65.5</v>
       </c>
       <c r="H64" t="n">
-        <v>65.5</v>
+        <v>63.73879800916023</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>1.761201990839766</v>
       </c>
       <c r="J64" t="n">
-        <v>124.284693877551</v>
+        <v>253.9616718512663</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -4608,13 +4608,13 @@
         <v>125.3051020408163</v>
       </c>
       <c r="M64" t="n">
-        <v>64.47959183673473</v>
+        <v>192.3953678196101</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>385.2934807256237</v>
+        <v>372.3198989898989</v>
       </c>
       <c r="P64" t="n">
         <v>1</v>
@@ -4646,7 +4646,7 @@
         <v>16</v>
       </c>
       <c r="D65" t="n">
-        <v>122.799</v>
+        <v>140.444</v>
       </c>
       <c r="E65" t="n">
         <v>41.57</v>
@@ -4658,28 +4658,28 @@
         <v>69.5</v>
       </c>
       <c r="H65" t="n">
-        <v>10.92067447287434</v>
+        <v>40</v>
       </c>
       <c r="I65" t="n">
-        <v>58.57932552712566</v>
+        <v>29.5</v>
       </c>
       <c r="J65" t="n">
-        <v>698.3102040816327</v>
+        <v>703.3102040816327</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>125.3051020408163</v>
+        <v>143.3102040816326</v>
       </c>
       <c r="M65" t="n">
-        <v>583.9257765136906</v>
+        <v>600.0000000000001</v>
       </c>
       <c r="N65" t="n">
         <v>-7.105427357601002e-15</v>
       </c>
       <c r="O65" t="n">
-        <v>963.3799994741773</v>
+        <v>966.319898989899</v>
       </c>
       <c r="P65" t="n">
         <v>1</v>
@@ -4723,13 +4723,13 @@
         <v>72</v>
       </c>
       <c r="H66" t="n">
-        <v>72</v>
+        <v>40.52040816326519</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>31.47959183673481</v>
       </c>
       <c r="J66" t="n">
-        <v>90.3001036026656</v>
+        <v>103.7897959183673</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -4738,13 +4738,13 @@
         <v>143.3102040816326</v>
       </c>
       <c r="M66" t="n">
-        <v>18.98989952103296</v>
+        <v>0.9999999999999158</v>
       </c>
       <c r="N66" t="n">
         <v>-7.105427357601002e-15</v>
       </c>
       <c r="O66" t="n">
-        <v>982.1799999999999</v>
+        <v>967.3098989898989</v>
       </c>
       <c r="P66" t="n">
         <v>1</v>
@@ -4794,7 +4794,7 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>68.80918367346938</v>
+        <v>83.82948772407644</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -4803,7 +4803,7 @@
         <v>125.3091836734694</v>
       </c>
       <c r="M67" t="n">
-        <v>18.00000000000005</v>
+        <v>33.02030405060717</v>
       </c>
       <c r="N67" t="n">
         <v>7.105427357601002e-15</v>
@@ -4841,7 +4841,7 @@
         <v>19</v>
       </c>
       <c r="D68" t="n">
-        <v>122.803</v>
+        <v>117.645</v>
       </c>
       <c r="E68" t="n">
         <v>43.091</v>
@@ -4865,19 +4865,19 @@
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>81.5</v>
+        <v>81.50000000000013</v>
       </c>
       <c r="M68" t="n">
-        <v>2.153159805333637e-14</v>
+        <v>-1.650755850755788e-13</v>
       </c>
       <c r="N68" t="n">
-        <v>42.93300000000001</v>
+        <v>37.77499999999988</v>
       </c>
       <c r="O68" t="n">
-        <v>956.6333333333333</v>
+        <v>961.8434343434343</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>-5.684341886080802e-16</v>
       </c>
       <c r="Q68" t="n">
         <v>47.87888888888889</v>
@@ -4930,19 +4930,19 @@
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>87.50000000000003</v>
+        <v>87.5</v>
       </c>
       <c r="M69" t="n">
-        <v>-7.177199351112125e-15</v>
+        <v>2.153159805333638e-14</v>
       </c>
       <c r="N69" t="n">
-        <v>31.89499999999997</v>
+        <v>31.895</v>
       </c>
       <c r="O69" t="n">
-        <v>924.4161616161616</v>
+        <v>929.6262626262626</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q69" t="n">
         <v>47.87888888888889</v>
@@ -5004,10 +5004,10 @@
         <v>36.09400000000002</v>
       </c>
       <c r="O70" t="n">
-        <v>887.9575757575757</v>
+        <v>893.1676767676767</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q70" t="n">
         <v>49.58333333333333</v>
@@ -5036,7 +5036,7 @@
         <v>22</v>
       </c>
       <c r="D71" t="n">
-        <v>119.884</v>
+        <v>110.043</v>
       </c>
       <c r="E71" t="n">
         <v>40.775</v>
@@ -5060,19 +5060,19 @@
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>79.50000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="M71" t="n">
-        <v>-1.4210854715202e-14</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>41.974</v>
+        <v>32.13300000000003</v>
       </c>
       <c r="O71" t="n">
-        <v>845.5595959595959</v>
+        <v>860.7101010101009</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q71" t="n">
         <v>45.30555555555555</v>
@@ -5134,10 +5134,10 @@
         <v>39.97300000000003</v>
       </c>
       <c r="O72" t="n">
-        <v>805.1828282828282</v>
+        <v>820.3333333333331</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q72" t="n">
         <v>45.30555555555555</v>
@@ -5190,19 +5190,19 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>57.50000000000001</v>
+        <v>57.5</v>
       </c>
       <c r="M73" t="n">
-        <v>-7.105427357601002e-15</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>45.79499999999998</v>
+        <v>45.79499999999999</v>
       </c>
       <c r="O73" t="n">
-        <v>758.9252525252524</v>
+        <v>774.0757575757574</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q73" t="n">
         <v>38.49777777777778</v>
@@ -5426,7 +5426,7 @@
         <v>4</v>
       </c>
       <c r="D77" t="n">
-        <v>68.551</v>
+        <v>68.483</v>
       </c>
       <c r="E77" t="n">
         <v>38.078</v>
@@ -5438,10 +5438,10 @@
         <v>143</v>
       </c>
       <c r="H77" t="n">
-        <v>70.95</v>
+        <v>70.88061224489796</v>
       </c>
       <c r="I77" t="n">
-        <v>72.05</v>
+        <v>72.11938775510204</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -5450,7 +5450,7 @@
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>69.95</v>
+        <v>69.88061224489796</v>
       </c>
       <c r="M77" t="n">
         <v>1</v>
@@ -5621,7 +5621,7 @@
         <v>7</v>
       </c>
       <c r="D80" t="n">
-        <v>75.066</v>
+        <v>84.11799999999999</v>
       </c>
       <c r="E80" t="n">
         <v>48.821</v>
@@ -5633,10 +5633,10 @@
         <v>139</v>
       </c>
       <c r="H80" t="n">
-        <v>77.59795918367345</v>
+        <v>86.83469387755099</v>
       </c>
       <c r="I80" t="n">
-        <v>61.40204081632655</v>
+        <v>52.16530612244901</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -5645,13 +5645,13 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>76.59795918367347</v>
+        <v>85.834693877551</v>
       </c>
       <c r="M80" t="n">
         <v>0.9999999999999858</v>
       </c>
       <c r="N80" t="n">
-        <v>-7.105427357601002e-15</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="O80" t="n">
         <v>124.95</v>
@@ -5816,7 +5816,7 @@
         <v>10</v>
       </c>
       <c r="D83" t="n">
-        <v>125.853</v>
+        <v>138.408</v>
       </c>
       <c r="E83" t="n">
         <v>45.383</v>
@@ -5828,10 +5828,10 @@
         <v>139.5</v>
       </c>
       <c r="H83" t="n">
-        <v>129.4214285714286</v>
+        <v>139.5</v>
       </c>
       <c r="I83" t="n">
-        <v>10.07857142857142</v>
+        <v>0</v>
       </c>
       <c r="J83" t="n">
         <v>-0</v>
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>128.4214285714285</v>
+        <v>139.5</v>
       </c>
       <c r="M83" t="n">
-        <v>1.000000000000002</v>
+        <v>-7.177199351112125e-15</v>
       </c>
       <c r="N83" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>1.697999999999986</v>
       </c>
       <c r="O83" t="n">
-        <v>127.9199999999999</v>
+        <v>125.2148484848484</v>
       </c>
       <c r="P83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
         <v>50.42555555555555</v>
@@ -5899,7 +5899,7 @@
         <v>142.5</v>
       </c>
       <c r="J84" t="n">
-        <v>275.144090669632</v>
+        <v>281.1437845784168</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -5908,13 +5908,13 @@
         <v>141.2326530612245</v>
       </c>
       <c r="M84" t="n">
-        <v>133.9114376084075</v>
+        <v>139.9111315171922</v>
       </c>
       <c r="N84" t="n">
         <v>7.105427357601002e-15</v>
       </c>
       <c r="O84" t="n">
-        <v>260.4923232323233</v>
+        <v>263.7268686868687</v>
       </c>
       <c r="P84" t="n">
         <v>1</v>
@@ -5979,7 +5979,7 @@
         <v>2.86699999999999</v>
       </c>
       <c r="O85" t="n">
-        <v>257.5963636363637</v>
+        <v>260.8309090909091</v>
       </c>
       <c r="P85" t="n">
         <v>0</v>
@@ -6011,7 +6011,7 @@
         <v>13</v>
       </c>
       <c r="D86" t="n">
-        <v>139.087</v>
+        <v>136.236</v>
       </c>
       <c r="E86" t="n">
         <v>56.911</v>
@@ -6023,19 +6023,19 @@
         <v>128</v>
       </c>
       <c r="H86" t="n">
-        <v>0.4797979797979181</v>
+        <v>0.4797979797979792</v>
       </c>
       <c r="I86" t="n">
-        <v>127.5202020202021</v>
+        <v>127.520202020202</v>
       </c>
       <c r="J86" t="n">
-        <v>142.4457122242837</v>
+        <v>139.5365285508143</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>141.9255102040816</v>
+        <v>139.0163265306122</v>
       </c>
       <c r="M86" t="n">
         <v>0.9999999999999949</v>
@@ -6044,7 +6044,7 @@
         <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>258.5863636363637</v>
+        <v>261.8209090909091</v>
       </c>
       <c r="P86" t="n">
         <v>1</v>
@@ -6088,10 +6088,10 @@
         <v>118.5</v>
       </c>
       <c r="H87" t="n">
-        <v>3.500000000000057</v>
+        <v>3.499999999999943</v>
       </c>
       <c r="I87" t="n">
-        <v>114.9999999999999</v>
+        <v>115.0000000000001</v>
       </c>
       <c r="J87" t="n">
         <v>134.4959183673469</v>
@@ -6103,13 +6103,13 @@
         <v>137.9959183673469</v>
       </c>
       <c r="M87" t="n">
-        <v>-1.435439870222425e-14</v>
+        <v>-7.177199351112123e-14</v>
       </c>
       <c r="N87" t="n">
         <v>1</v>
       </c>
       <c r="O87" t="n">
-        <v>257.5762626262627</v>
+        <v>260.810808080808</v>
       </c>
       <c r="P87" t="n">
         <v>-0</v>
@@ -6159,25 +6159,25 @@
         <v>132.5</v>
       </c>
       <c r="J88" t="n">
-        <v>124.284693877551</v>
+        <v>253.9616718512663</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>124.284693877551</v>
+        <v>125.3051020408163</v>
       </c>
       <c r="M88" t="n">
-        <v>2.87087974044485e-14</v>
+        <v>128.65656981045</v>
       </c>
       <c r="N88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>256.5661616161617</v>
+        <v>388.1808121931535</v>
       </c>
       <c r="P88" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="Q88" t="n">
         <v>59.53444444444445</v>
@@ -6206,7 +6206,7 @@
         <v>16</v>
       </c>
       <c r="D89" t="n">
-        <v>122.799</v>
+        <v>140.444</v>
       </c>
       <c r="E89" t="n">
         <v>41.57</v>
@@ -6224,22 +6224,22 @@
         <v>152.5</v>
       </c>
       <c r="J89" t="n">
-        <v>698.3102040816327</v>
+        <v>703.3102040816327</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>125.3051020408163</v>
+        <v>143.3102040816326</v>
       </c>
       <c r="M89" t="n">
-        <v>573.0051020408163</v>
+        <v>560.0000000000001</v>
       </c>
       <c r="N89" t="n">
         <v>-7.105427357601002e-15</v>
       </c>
       <c r="O89" t="n">
-        <v>823.8412126365698</v>
+        <v>942.5808121931535</v>
       </c>
       <c r="P89" t="n">
         <v>1</v>
@@ -6283,13 +6283,13 @@
         <v>170.5</v>
       </c>
       <c r="H90" t="n">
-        <v>54.01010047896709</v>
+        <v>48.87458569429873</v>
       </c>
       <c r="I90" t="n">
-        <v>116.4898995210329</v>
+        <v>121.6254143057013</v>
       </c>
       <c r="J90" t="n">
-        <v>90.3001036026656</v>
+        <v>103.7897959183673</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
@@ -6298,13 +6298,13 @@
         <v>143.3102040816326</v>
       </c>
       <c r="M90" t="n">
-        <v>1.000000000000031</v>
+        <v>9.354177531033356</v>
       </c>
       <c r="N90" t="n">
         <v>-7.105427357601002e-15</v>
       </c>
       <c r="O90" t="n">
-        <v>824.8312126365698</v>
+        <v>951.8414479488765</v>
       </c>
       <c r="P90" t="n">
         <v>1</v>
@@ -6348,31 +6348,31 @@
         <v>174</v>
       </c>
       <c r="H91" t="n">
-        <v>147.5820466049902</v>
+        <v>40.45928778612767</v>
       </c>
       <c r="I91" t="n">
-        <v>26.41795339500982</v>
+        <v>133.5407122138723</v>
       </c>
       <c r="J91" t="n">
-        <v>68.80918367346938</v>
+        <v>83.82948772407644</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>125.3091836734694</v>
+        <v>124.2887755102041</v>
       </c>
       <c r="M91" t="n">
-        <v>91.08204660499015</v>
+        <v>8.612639221334548e-14</v>
       </c>
       <c r="N91" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>0.9999999999999929</v>
       </c>
       <c r="O91" t="n">
-        <v>915.0024387755101</v>
+        <v>950.8313469387756</v>
       </c>
       <c r="P91" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="Q91" t="n">
         <v>54.18555555555556</v>
@@ -6401,7 +6401,7 @@
         <v>19</v>
       </c>
       <c r="D92" t="n">
-        <v>122.803</v>
+        <v>117.645</v>
       </c>
       <c r="E92" t="n">
         <v>43.091</v>
@@ -6413,10 +6413,10 @@
         <v>162.5</v>
       </c>
       <c r="H92" t="n">
-        <v>162.5</v>
+        <v>121.045918367347</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>41.45408163265301</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -6425,16 +6425,16 @@
         <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>125.3091836734694</v>
+        <v>120.0459183673469</v>
       </c>
       <c r="M92" t="n">
-        <v>37.1908163265306</v>
+        <v>1.000000000000016</v>
       </c>
       <c r="N92" t="n">
         <v>7.105427357601002e-15</v>
       </c>
       <c r="O92" t="n">
-        <v>951.8213469387754</v>
+        <v>951.8213469387756</v>
       </c>
       <c r="P92" t="n">
         <v>1</v>
@@ -6493,13 +6493,13 @@
         <v>120.0459183673469</v>
       </c>
       <c r="M93" t="n">
-        <v>20.95408163265309</v>
+        <v>20.95408163265297</v>
       </c>
       <c r="N93" t="n">
         <v>7.105427357601002e-15</v>
       </c>
       <c r="O93" t="n">
-        <v>972.5658877551019</v>
+        <v>972.565887755102</v>
       </c>
       <c r="P93" t="n">
         <v>1</v>
@@ -6564,7 +6564,7 @@
         <v>-7.105427357601002e-15</v>
       </c>
       <c r="O94" t="n">
-        <v>973.5558877551019</v>
+        <v>973.555887755102</v>
       </c>
       <c r="P94" t="n">
         <v>1</v>
@@ -6596,7 +6596,7 @@
         <v>22</v>
       </c>
       <c r="D95" t="n">
-        <v>119.884</v>
+        <v>110.043</v>
       </c>
       <c r="E95" t="n">
         <v>40.775</v>
@@ -6608,10 +6608,10 @@
         <v>132</v>
       </c>
       <c r="H95" t="n">
-        <v>123.330612244898</v>
+        <v>113.2887755102041</v>
       </c>
       <c r="I95" t="n">
-        <v>8.669387755102036</v>
+        <v>18.71122448979588</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -6620,10 +6620,10 @@
         <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>122.330612244898</v>
+        <v>112.2887755102041</v>
       </c>
       <c r="M95" t="n">
-        <v>1</v>
+        <v>1.000000000000014</v>
       </c>
       <c r="N95" t="n">
         <v>7.105427357601002e-15</v>
@@ -6986,7 +6986,7 @@
         <v>4</v>
       </c>
       <c r="D101" t="n">
-        <v>68.551</v>
+        <v>68.483</v>
       </c>
       <c r="E101" t="n">
         <v>38.078</v>
@@ -7007,22 +7007,22 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>57.44979591836737</v>
+        <v>57.38040816326532</v>
       </c>
       <c r="L101" t="n">
-        <v>67.94979591836729</v>
+        <v>67.8804081632653</v>
       </c>
       <c r="M101" t="n">
-        <v>8.526512829121202e-14</v>
+        <v>2.131628207280301e-14</v>
       </c>
       <c r="N101" t="n">
-        <v>1.960200000000054</v>
+        <v>1.960200000000011</v>
       </c>
       <c r="O101" t="n">
         <v>120</v>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q101" t="n">
         <v>42.30888888888889</v>
@@ -7072,19 +7072,19 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>108.4933558424899</v>
+        <v>108.4933558424901</v>
       </c>
       <c r="L102" t="n">
-        <v>69.88061224489796</v>
+        <v>69.8806122448979</v>
       </c>
       <c r="M102" t="n">
-        <v>55.11274359759192</v>
+        <v>55.1127435975922</v>
       </c>
       <c r="N102" t="n">
-        <v>-3.552713678800501e-15</v>
+        <v>5.329070518200751e-14</v>
       </c>
       <c r="O102" t="n">
-        <v>174.561616161616</v>
+        <v>174.5616161616162</v>
       </c>
       <c r="P102" t="n">
         <v>1</v>
@@ -7140,19 +7140,19 @@
         <v>0</v>
       </c>
       <c r="L103" t="n">
-        <v>22.50000000000001</v>
+        <v>22.5</v>
       </c>
       <c r="M103" t="n">
-        <v>-3.229739708000455e-14</v>
+        <v>-4.66517957822288e-14</v>
       </c>
       <c r="N103" t="n">
-        <v>53.01599999999998</v>
+        <v>53.016</v>
       </c>
       <c r="O103" t="n">
-        <v>121.0101010101009</v>
+        <v>121.010101010101</v>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q103" t="n">
         <v>42.30888888888889</v>
@@ -7181,7 +7181,7 @@
         <v>7</v>
       </c>
       <c r="D104" t="n">
-        <v>75.066</v>
+        <v>84.11799999999999</v>
       </c>
       <c r="E104" t="n">
         <v>48.821</v>
@@ -7202,16 +7202,16 @@
         <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>52.07755102040831</v>
+        <v>61.3142857142857</v>
       </c>
       <c r="L104" t="n">
-        <v>75.57755102040819</v>
+        <v>84.8142857142857</v>
       </c>
       <c r="M104" t="n">
-        <v>1.13686837721616e-13</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>0.9999999999999645</v>
+        <v>1.000000000000007</v>
       </c>
       <c r="O104" t="n">
         <v>120</v>
@@ -7267,22 +7267,22 @@
         <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>299.6536409237708</v>
+        <v>312.4635582791427</v>
       </c>
       <c r="L105" t="n">
-        <v>85.83469387755106</v>
+        <v>85.83469387755102</v>
       </c>
       <c r="M105" t="n">
-        <v>234.3189470462198</v>
+        <v>247.1288644015917</v>
       </c>
       <c r="N105" t="n">
-        <v>-4.973799150320701e-14</v>
+        <v>-7.105427357601002e-15</v>
       </c>
       <c r="O105" t="n">
-        <v>351.9757575757576</v>
+        <v>364.6575757575758</v>
       </c>
       <c r="P105" t="n">
-        <v>1</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="Q105" t="n">
         <v>54.24555555555555</v>
@@ -7344,7 +7344,7 @@
         <v>111.153</v>
       </c>
       <c r="O106" t="n">
-        <v>239.7</v>
+        <v>252.3818181818182</v>
       </c>
       <c r="P106" t="n">
         <v>-0</v>
@@ -7376,7 +7376,7 @@
         <v>10</v>
       </c>
       <c r="D107" t="n">
-        <v>125.853</v>
+        <v>138.408</v>
       </c>
       <c r="E107" t="n">
         <v>45.383</v>
@@ -7400,13 +7400,13 @@
         <v>0</v>
       </c>
       <c r="L107" t="n">
-        <v>7.499999999999997</v>
+        <v>7.499999999999983</v>
       </c>
       <c r="M107" t="n">
-        <v>-3.588599675556061e-14</v>
+        <v>7.177199351112124e-15</v>
       </c>
       <c r="N107" t="n">
-        <v>118.503</v>
+        <v>131.058</v>
       </c>
       <c r="O107" t="n">
         <v>120</v>
@@ -7459,22 +7459,22 @@
         <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>275.144090669632</v>
+        <v>281.1437845784168</v>
       </c>
       <c r="K108" t="n">
-        <v>0.9998979695948833</v>
+        <v>0</v>
       </c>
       <c r="L108" t="n">
         <v>141.2326530612245</v>
       </c>
       <c r="M108" t="n">
-        <v>138.9113355780023</v>
+        <v>143.9111315171922</v>
       </c>
       <c r="N108" t="n">
         <v>7.105427357601002e-15</v>
       </c>
       <c r="O108" t="n">
-        <v>257.5222222222222</v>
+        <v>262.4720202020203</v>
       </c>
       <c r="P108" t="n">
         <v>1</v>
@@ -7530,16 +7530,16 @@
         <v>0</v>
       </c>
       <c r="L109" t="n">
-        <v>2.999999999999988</v>
+        <v>3</v>
       </c>
       <c r="M109" t="n">
-        <v>1.076579902666819e-14</v>
+        <v>-8.971499188890156e-16</v>
       </c>
       <c r="N109" t="n">
         <v>136.147</v>
       </c>
       <c r="O109" t="n">
-        <v>120</v>
+        <v>124.9497979797981</v>
       </c>
       <c r="P109" t="n">
         <v>0</v>
@@ -7571,7 +7571,7 @@
         <v>13</v>
       </c>
       <c r="D110" t="n">
-        <v>139.087</v>
+        <v>136.236</v>
       </c>
       <c r="E110" t="n">
         <v>56.911</v>
@@ -7589,22 +7589,22 @@
         <v>0</v>
       </c>
       <c r="J110" t="n">
-        <v>142.4457122242837</v>
+        <v>139.5365285508143</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
       </c>
       <c r="L110" t="n">
-        <v>141.9255102040816</v>
+        <v>139.0163265306122</v>
       </c>
       <c r="M110" t="n">
-        <v>3.020202020202029</v>
+        <v>3.020202020201972</v>
       </c>
       <c r="N110" t="n">
         <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>122.99</v>
+        <v>127.939797979798</v>
       </c>
       <c r="P110" t="n">
         <v>1</v>
@@ -7660,16 +7660,16 @@
         <v>0</v>
       </c>
       <c r="L111" t="n">
-        <v>136.4959183673469</v>
+        <v>136.495918367347</v>
       </c>
       <c r="M111" t="n">
-        <v>-1.435439870222425e-14</v>
+        <v>-4.306319610667274e-14</v>
       </c>
       <c r="N111" t="n">
-        <v>2.470000000000027</v>
+        <v>2.46999999999997</v>
       </c>
       <c r="O111" t="n">
-        <v>120.4950505050505</v>
+        <v>125.4448484848485</v>
       </c>
       <c r="P111" t="n">
         <v>0</v>
@@ -7719,7 +7719,7 @@
         <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>124.284693877551</v>
+        <v>253.9616718512663</v>
       </c>
       <c r="K112" t="n">
         <v>0</v>
@@ -7728,13 +7728,13 @@
         <v>125.3051020408163</v>
       </c>
       <c r="M112" t="n">
-        <v>1.479591836734705</v>
+        <v>131.1565698104499</v>
       </c>
       <c r="N112" t="n">
         <v>0</v>
       </c>
       <c r="O112" t="n">
-        <v>121.9598464234179</v>
+        <v>255.289852597194</v>
       </c>
       <c r="P112" t="n">
         <v>1</v>
@@ -7766,7 +7766,7 @@
         <v>16</v>
       </c>
       <c r="D113" t="n">
-        <v>122.799</v>
+        <v>140.444</v>
       </c>
       <c r="E113" t="n">
         <v>41.57</v>
@@ -7784,22 +7784,22 @@
         <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>698.3102040816327</v>
+        <v>703.3102040816327</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
       </c>
       <c r="L113" t="n">
-        <v>125.3051020408163</v>
+        <v>143.3102040816326</v>
       </c>
       <c r="M113" t="n">
-        <v>579.0051020408163</v>
+        <v>566.0000000000001</v>
       </c>
       <c r="N113" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>-7.105427357601002e-15</v>
       </c>
       <c r="O113" t="n">
-        <v>695.174897443826</v>
+        <v>815.629852597194</v>
       </c>
       <c r="P113" t="n">
         <v>1</v>
@@ -7849,25 +7849,25 @@
         <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>90.3001036026656</v>
+        <v>103.7897959183673</v>
       </c>
       <c r="K114" t="n">
         <v>0</v>
       </c>
       <c r="L114" t="n">
-        <v>102.8001036026656</v>
+        <v>116.2897959183672</v>
       </c>
       <c r="M114" t="n">
-        <v>-5.024039545778486e-14</v>
+        <v>-3.588599675556061e-14</v>
       </c>
       <c r="N114" t="n">
-        <v>39.6998984693877</v>
+        <v>26.48000000000015</v>
       </c>
       <c r="O114" t="n">
-        <v>655.0739898989899</v>
+        <v>788.8823778497191</v>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q114" t="n">
         <v>46.18888888888889</v>
@@ -7914,22 +7914,22 @@
         <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>68.80918367346938</v>
+        <v>83.82948772407644</v>
       </c>
       <c r="K115" t="n">
         <v>0</v>
       </c>
       <c r="L115" t="n">
-        <v>85.80918367346922</v>
+        <v>100.8294877240764</v>
       </c>
       <c r="M115" t="n">
-        <v>1.004807909155697e-13</v>
+        <v>1.435439870222425e-14</v>
       </c>
       <c r="N115" t="n">
-        <v>38.71000000000016</v>
+        <v>23.99010203040508</v>
       </c>
       <c r="O115" t="n">
-        <v>615.9729797979797</v>
+        <v>764.6499515563806</v>
       </c>
       <c r="P115" t="n">
         <v>0</v>
@@ -7961,7 +7961,7 @@
         <v>19</v>
       </c>
       <c r="D116" t="n">
-        <v>122.803</v>
+        <v>117.645</v>
       </c>
       <c r="E116" t="n">
         <v>43.091</v>
@@ -7982,19 +7982,19 @@
         <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>306.669146942524</v>
+        <v>141.186310122457</v>
       </c>
       <c r="L116" t="n">
-        <v>125.3091836734694</v>
+        <v>120.045918367347</v>
       </c>
       <c r="M116" t="n">
-        <v>199.8599632690545</v>
+        <v>39.64039175511005</v>
       </c>
       <c r="N116" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>-7.105427357601002e-15</v>
       </c>
       <c r="O116" t="n">
-        <v>813.8343434343437</v>
+        <v>803.8939393939396</v>
       </c>
       <c r="P116" t="n">
         <v>1</v>
@@ -8050,16 +8050,16 @@
         <v>0</v>
       </c>
       <c r="L117" t="n">
-        <v>17.49999999999988</v>
+        <v>17.49999999999999</v>
       </c>
       <c r="M117" t="n">
         <v>-7.177199351112125e-15</v>
       </c>
       <c r="N117" t="n">
-        <v>100.4950000000001</v>
+        <v>100.495</v>
       </c>
       <c r="O117" t="n">
-        <v>712.3242424242426</v>
+        <v>702.3838383838386</v>
       </c>
       <c r="P117" t="n">
         <v>0</v>
@@ -8124,7 +8124,7 @@
         <v>105.184</v>
       </c>
       <c r="O118" t="n">
-        <v>606.0777777777779</v>
+        <v>596.1373737373739</v>
       </c>
       <c r="P118" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
         <v>22</v>
       </c>
       <c r="D119" t="n">
-        <v>119.884</v>
+        <v>110.043</v>
       </c>
       <c r="E119" t="n">
         <v>40.775</v>
@@ -8186,7 +8186,7 @@
         <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>104.694</v>
+        <v>94.85300000000002</v>
       </c>
       <c r="O119" t="n">
         <v>500.3262626262627</v>
@@ -8502,13 +8502,13 @@
         <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>53.47030405060711</v>
+        <v>53.47030405060709</v>
       </c>
       <c r="L124" t="n">
         <v>69.95</v>
       </c>
       <c r="M124" t="n">
-        <v>1.020304050607109</v>
+        <v>1.020304050607088</v>
       </c>
       <c r="N124" t="n">
         <v>3.552713678800501e-15</v>
@@ -8546,7 +8546,7 @@
         <v>4</v>
       </c>
       <c r="D125" t="n">
-        <v>68.551</v>
+        <v>68.483</v>
       </c>
       <c r="E125" t="n">
         <v>38.078</v>
@@ -8567,10 +8567,10 @@
         <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>47.9295918367347</v>
+        <v>47.86020408163266</v>
       </c>
       <c r="L125" t="n">
-        <v>68.9295918367347</v>
+        <v>68.86020408163266</v>
       </c>
       <c r="M125" t="n">
         <v>0</v>
@@ -8632,19 +8632,19 @@
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>449.2126701981679</v>
+        <v>471.2583798196352</v>
       </c>
       <c r="L126" t="n">
         <v>69.88061224489796</v>
       </c>
       <c r="M126" t="n">
-        <v>405.83205795327</v>
+        <v>427.8777675747372</v>
       </c>
       <c r="N126" t="n">
         <v>-3.552713678800501e-15</v>
       </c>
       <c r="O126" t="n">
-        <v>521.7737373737373</v>
+        <v>543.5989898989899</v>
       </c>
       <c r="P126" t="n">
         <v>1</v>
@@ -8709,7 +8709,7 @@
         <v>46.646</v>
       </c>
       <c r="O127" t="n">
-        <v>474.6565656565656</v>
+        <v>496.4818181818182</v>
       </c>
       <c r="P127" t="n">
         <v>0</v>
@@ -8741,7 +8741,7 @@
         <v>7</v>
       </c>
       <c r="D128" t="n">
-        <v>75.066</v>
+        <v>84.11799999999999</v>
       </c>
       <c r="E128" t="n">
         <v>48.821</v>
@@ -8771,10 +8771,10 @@
         <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>48.116</v>
+        <v>57.16799999999999</v>
       </c>
       <c r="O128" t="n">
-        <v>426.0545454545454</v>
+        <v>438.7363636363636</v>
       </c>
       <c r="P128" t="n">
         <v>0</v>
@@ -8839,7 +8839,7 @@
         <v>62.06799999999998</v>
       </c>
       <c r="O129" t="n">
-        <v>363.3595959595959</v>
+        <v>376.0414141414142</v>
       </c>
       <c r="P129" t="n">
         <v>0</v>
@@ -8904,7 +8904,7 @@
         <v>117.523</v>
       </c>
       <c r="O130" t="n">
-        <v>244.649494949495</v>
+        <v>257.3313131313132</v>
       </c>
       <c r="P130" t="n">
         <v>0</v>
@@ -8936,7 +8936,7 @@
         <v>10</v>
       </c>
       <c r="D131" t="n">
-        <v>125.853</v>
+        <v>138.408</v>
       </c>
       <c r="E131" t="n">
         <v>45.383</v>
@@ -8960,13 +8960,13 @@
         <v>0</v>
       </c>
       <c r="L131" t="n">
-        <v>2.499999999999995</v>
+        <v>2.500000000000023</v>
       </c>
       <c r="M131" t="n">
-        <v>-2.691449756667046e-15</v>
+        <v>-3.095167220167103e-14</v>
       </c>
       <c r="N131" t="n">
-        <v>123.403</v>
+        <v>135.958</v>
       </c>
       <c r="O131" t="n">
         <v>120</v>
@@ -9019,7 +9019,7 @@
         <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>275.144090669632</v>
+        <v>281.1437845784168</v>
       </c>
       <c r="K132" t="n">
         <v>0</v>
@@ -9028,13 +9028,13 @@
         <v>141.2326530612245</v>
       </c>
       <c r="M132" t="n">
-        <v>134.4114376084074</v>
+        <v>140.4111315171922</v>
       </c>
       <c r="N132" t="n">
         <v>7.105427357601002e-15</v>
       </c>
       <c r="O132" t="n">
-        <v>253.0673232323233</v>
+        <v>259.0070202020203</v>
       </c>
       <c r="P132" t="n">
         <v>1</v>
@@ -9087,16 +9087,16 @@
         <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>6.500357142857061</v>
+        <v>0.5000510204081071</v>
       </c>
       <c r="L133" t="n">
-        <v>7.500357142857061</v>
+        <v>1.500051020408107</v>
       </c>
       <c r="M133" t="n">
-        <v>-1.794299837778031e-15</v>
+        <v>2.915737236389301e-15</v>
       </c>
       <c r="N133" t="n">
-        <v>131.7366500000001</v>
+        <v>137.61695</v>
       </c>
       <c r="O133" t="n">
         <v>120</v>
@@ -9131,7 +9131,7 @@
         <v>13</v>
       </c>
       <c r="D134" t="n">
-        <v>139.087</v>
+        <v>136.236</v>
       </c>
       <c r="E134" t="n">
         <v>56.911</v>
@@ -9149,16 +9149,16 @@
         <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>142.4457122242837</v>
+        <v>139.5365285508143</v>
       </c>
       <c r="K134" t="n">
         <v>0</v>
       </c>
       <c r="L134" t="n">
-        <v>141.9255102040816</v>
+        <v>139.0163265306122</v>
       </c>
       <c r="M134" t="n">
-        <v>2.02020202020202</v>
+        <v>2.020202020202006</v>
       </c>
       <c r="N134" t="n">
         <v>0</v>
@@ -9223,10 +9223,10 @@
         <v>136.9959183673469</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>-1.435439870222425e-14</v>
       </c>
       <c r="N135" t="n">
-        <v>1.980000000000018</v>
+        <v>1.97999999999999</v>
       </c>
       <c r="O135" t="n">
         <v>120</v>
@@ -9279,7 +9279,7 @@
         <v>0</v>
       </c>
       <c r="J136" t="n">
-        <v>124.284693877551</v>
+        <v>253.9616718512663</v>
       </c>
       <c r="K136" t="n">
         <v>0</v>
@@ -9288,13 +9288,13 @@
         <v>125.3051020408163</v>
       </c>
       <c r="M136" t="n">
-        <v>5.479591836734699</v>
+        <v>135.1565698104499</v>
       </c>
       <c r="N136" t="n">
         <v>0</v>
       </c>
       <c r="O136" t="n">
-        <v>125.4247959183674</v>
+        <v>253.8050041123454</v>
       </c>
       <c r="P136" t="n">
         <v>1</v>
@@ -9326,7 +9326,7 @@
         <v>16</v>
       </c>
       <c r="D137" t="n">
-        <v>122.799</v>
+        <v>140.444</v>
       </c>
       <c r="E137" t="n">
         <v>41.57</v>
@@ -9344,22 +9344,22 @@
         <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>698.3102040816327</v>
+        <v>703.3102040816327</v>
       </c>
       <c r="K137" t="n">
         <v>0</v>
       </c>
       <c r="L137" t="n">
-        <v>125.3051020408163</v>
+        <v>143.3102040816326</v>
       </c>
       <c r="M137" t="n">
-        <v>583.5051020408164</v>
+        <v>570.5000000000001</v>
       </c>
       <c r="N137" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>-7.105427357601002e-15</v>
       </c>
       <c r="O137" t="n">
-        <v>703.0948469387755</v>
+        <v>818.6000041123455</v>
       </c>
       <c r="P137" t="n">
         <v>1</v>
@@ -9409,25 +9409,25 @@
         <v>0</v>
       </c>
       <c r="J138" t="n">
-        <v>90.3001036026656</v>
+        <v>103.7897959183673</v>
       </c>
       <c r="K138" t="n">
         <v>0</v>
       </c>
       <c r="L138" t="n">
-        <v>100.8001036026656</v>
+        <v>114.2897959183672</v>
       </c>
       <c r="M138" t="n">
-        <v>5.024039545778486e-14</v>
+        <v>-1.076579902666819e-13</v>
       </c>
       <c r="N138" t="n">
-        <v>41.65989846938772</v>
+        <v>28.44000000000013</v>
       </c>
       <c r="O138" t="n">
-        <v>661.0141414141415</v>
+        <v>789.8727313850725</v>
       </c>
       <c r="P138" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q138" t="n">
         <v>46.18888888888889</v>
@@ -9474,22 +9474,22 @@
         <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>68.80918367346938</v>
+        <v>83.82948772407644</v>
       </c>
       <c r="K139" t="n">
         <v>0</v>
       </c>
       <c r="L139" t="n">
-        <v>83.30918367346935</v>
+        <v>98.32948772407644</v>
       </c>
       <c r="M139" t="n">
-        <v>-1.435439870222425e-14</v>
+        <v>2.870879740444849e-14</v>
       </c>
       <c r="N139" t="n">
-        <v>41.16000000000003</v>
+        <v>26.44010203040508</v>
       </c>
       <c r="O139" t="n">
-        <v>619.4383838383839</v>
+        <v>763.1655576169866</v>
       </c>
       <c r="P139" t="n">
         <v>0</v>
@@ -9521,7 +9521,7 @@
         <v>19</v>
       </c>
       <c r="D140" t="n">
-        <v>122.803</v>
+        <v>117.645</v>
       </c>
       <c r="E140" t="n">
         <v>43.091</v>
@@ -9545,19 +9545,19 @@
         <v>0</v>
       </c>
       <c r="L140" t="n">
-        <v>30.00000000000006</v>
+        <v>30</v>
       </c>
       <c r="M140" t="n">
-        <v>2.153159805333637e-14</v>
+        <v>2.512019772889244e-14</v>
       </c>
       <c r="N140" t="n">
-        <v>93.40299999999996</v>
+        <v>88.245</v>
       </c>
       <c r="O140" t="n">
-        <v>525.0919191919193</v>
+        <v>674.0291939806229</v>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q140" t="n">
         <v>47.87888888888889</v>
@@ -9610,19 +9610,19 @@
         <v>0</v>
       </c>
       <c r="L141" t="n">
-        <v>39.00000000000001</v>
+        <v>38.99999999999999</v>
       </c>
       <c r="M141" t="n">
-        <v>-1.435439870222425e-14</v>
+        <v>-1.14835189617794e-13</v>
       </c>
       <c r="N141" t="n">
-        <v>79.425</v>
+        <v>79.42500000000001</v>
       </c>
       <c r="O141" t="n">
-        <v>444.8646464646465</v>
+        <v>593.8019212533501</v>
       </c>
       <c r="P141" t="n">
-        <v>0</v>
+        <v>-1.820416506923185e-16</v>
       </c>
       <c r="Q141" t="n">
         <v>47.87888888888889</v>
@@ -9684,10 +9684,10 @@
         <v>79.70400000000001</v>
       </c>
       <c r="O142" t="n">
-        <v>364.3555555555556</v>
+        <v>513.2928303442592</v>
       </c>
       <c r="P142" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q142" t="n">
         <v>49.58333333333333</v>
@@ -9716,7 +9716,7 @@
         <v>22</v>
       </c>
       <c r="D143" t="n">
-        <v>119.884</v>
+        <v>110.043</v>
       </c>
       <c r="E143" t="n">
         <v>40.775</v>
@@ -9740,19 +9740,19 @@
         <v>0</v>
       </c>
       <c r="L143" t="n">
-        <v>37</v>
+        <v>36.99999999999999</v>
       </c>
       <c r="M143" t="n">
-        <v>0</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="N143" t="n">
-        <v>83.62400000000001</v>
+        <v>73.78300000000004</v>
       </c>
       <c r="O143" t="n">
-        <v>279.8868686868688</v>
+        <v>438.7645475159763</v>
       </c>
       <c r="P143" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q143" t="n">
         <v>45.30555555555555</v>
@@ -9814,10 +9814,10 @@
         <v>80.15300000000002</v>
       </c>
       <c r="O144" t="n">
-        <v>198.9242424242424</v>
+        <v>357.80192125335</v>
       </c>
       <c r="P144" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q144" t="n">
         <v>45.30555555555555</v>
@@ -9879,10 +9879,10 @@
         <v>78.13499999999999</v>
       </c>
       <c r="O145" t="n">
-        <v>120</v>
+        <v>278.8776788291076</v>
       </c>
       <c r="P145" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q145" t="n">
         <v>38.49777777777778</v>
@@ -10573,13 +10573,13 @@
         <v>63.5</v>
       </c>
       <c r="H156" t="n">
-        <v>20.50674743726694</v>
+        <v>0</v>
       </c>
       <c r="I156" t="n">
-        <v>42.99325256273306</v>
+        <v>63.5</v>
       </c>
       <c r="J156" t="n">
-        <v>275.144090669632</v>
+        <v>281.1437845784168</v>
       </c>
       <c r="K156" t="n">
         <v>0</v>
@@ -10588,13 +10588,13 @@
         <v>141.2326530612245</v>
       </c>
       <c r="M156" t="n">
-        <v>154.4181850456744</v>
+        <v>139.9111315171922</v>
       </c>
       <c r="N156" t="n">
         <v>7.105427357601002e-15</v>
       </c>
       <c r="O156" t="n">
-        <v>273.8640031952176</v>
+        <v>259.5020202020203</v>
       </c>
       <c r="P156" t="n">
         <v>1</v>
@@ -10650,16 +10650,16 @@
         <v>0</v>
       </c>
       <c r="L157" t="n">
-        <v>67.00000000000007</v>
+        <v>67</v>
       </c>
       <c r="M157" t="n">
-        <v>-4.306319610667274e-14</v>
+        <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>73.42699999999992</v>
+        <v>73.42699999999999</v>
       </c>
       <c r="O157" t="n">
-        <v>199.6953163265308</v>
+        <v>185.3333333333334</v>
       </c>
       <c r="P157" t="n">
         <v>0</v>
@@ -10703,13 +10703,13 @@
         <v>68</v>
       </c>
       <c r="H158" t="n">
-        <v>68</v>
+        <v>0.4797979797979792</v>
       </c>
       <c r="I158" t="n">
-        <v>0</v>
+        <v>67.52020202020202</v>
       </c>
       <c r="J158" t="n">
-        <v>142.4457122242837</v>
+        <v>139.5365285508143</v>
       </c>
       <c r="K158" t="n">
         <v>0</v>
@@ -10718,13 +10718,13 @@
         <v>139.0163265306122</v>
       </c>
       <c r="M158" t="n">
-        <v>71.42938569367141</v>
+        <v>0.9999999999999949</v>
       </c>
       <c r="N158" t="n">
         <v>0</v>
       </c>
       <c r="O158" t="n">
-        <v>270.4104081632655</v>
+        <v>186.3233333333334</v>
       </c>
       <c r="P158" t="n">
         <v>1</v>
@@ -10768,10 +10768,10 @@
         <v>70</v>
       </c>
       <c r="H159" t="n">
-        <v>70</v>
+        <v>58.75956536109649</v>
       </c>
       <c r="I159" t="n">
-        <v>0</v>
+        <v>11.24043463890351</v>
       </c>
       <c r="J159" t="n">
         <v>134.4959183673469</v>
@@ -10783,13 +10783,13 @@
         <v>139.0163265306122</v>
       </c>
       <c r="M159" t="n">
-        <v>65.47959183673466</v>
+        <v>54.23915719783119</v>
       </c>
       <c r="N159" t="n">
         <v>0</v>
       </c>
       <c r="O159" t="n">
-        <v>335.2352040816328</v>
+        <v>240.0200989591863</v>
       </c>
       <c r="P159" t="n">
         <v>1</v>
@@ -10833,13 +10833,13 @@
         <v>70.5</v>
       </c>
       <c r="H160" t="n">
+        <v>0</v>
+      </c>
+      <c r="I160" t="n">
         <v>70.5</v>
       </c>
-      <c r="I160" t="n">
-        <v>0</v>
-      </c>
       <c r="J160" t="n">
-        <v>124.284693877551</v>
+        <v>253.9616718512663</v>
       </c>
       <c r="K160" t="n">
         <v>0</v>
@@ -10848,13 +10848,13 @@
         <v>125.3051020408163</v>
       </c>
       <c r="M160" t="n">
-        <v>69.47959183673471</v>
+        <v>128.6565698104499</v>
       </c>
       <c r="N160" t="n">
         <v>0</v>
       </c>
       <c r="O160" t="n">
-        <v>404.0200000000002</v>
+        <v>367.3901030715317</v>
       </c>
       <c r="P160" t="n">
         <v>1</v>
@@ -10898,13 +10898,13 @@
         <v>67.5</v>
       </c>
       <c r="H161" t="n">
-        <v>45.00000000000007</v>
+        <v>39.99999999999989</v>
       </c>
       <c r="I161" t="n">
-        <v>22.49999999999993</v>
+        <v>27.50000000000011</v>
       </c>
       <c r="J161" t="n">
-        <v>698.3102040816327</v>
+        <v>703.3102040816327</v>
       </c>
       <c r="K161" t="n">
         <v>0</v>
@@ -10919,7 +10919,7 @@
         <v>-7.105427357601002e-15</v>
       </c>
       <c r="O161" t="n">
-        <v>998.02</v>
+        <v>961.3901030715316</v>
       </c>
       <c r="P161" t="n">
         <v>1</v>
@@ -10963,13 +10963,13 @@
         <v>62.5</v>
       </c>
       <c r="H162" t="n">
-        <v>54.01010047896703</v>
+        <v>62.5</v>
       </c>
       <c r="I162" t="n">
-        <v>8.489899521032967</v>
+        <v>0</v>
       </c>
       <c r="J162" t="n">
-        <v>90.3001036026656</v>
+        <v>103.7897959183673</v>
       </c>
       <c r="K162" t="n">
         <v>0</v>
@@ -10978,13 +10978,13 @@
         <v>143.3102040816326</v>
       </c>
       <c r="M162" t="n">
-        <v>1.000000000000031</v>
+        <v>22.97959183673471</v>
       </c>
       <c r="N162" t="n">
         <v>-7.105427357601002e-15</v>
       </c>
       <c r="O162" t="n">
-        <v>999.01</v>
+        <v>984.1398989898989</v>
       </c>
       <c r="P162" t="n">
         <v>1</v>
@@ -11034,7 +11034,7 @@
         <v>0</v>
       </c>
       <c r="J163" t="n">
-        <v>68.80918367346938</v>
+        <v>83.82948772407644</v>
       </c>
       <c r="K163" t="n">
         <v>0</v>
@@ -11043,7 +11043,7 @@
         <v>125.3091836734694</v>
       </c>
       <c r="M163" t="n">
-        <v>1.000000000000009</v>
+        <v>16.02030405060713</v>
       </c>
       <c r="N163" t="n">
         <v>7.105427357601002e-15</v>
@@ -11105,19 +11105,19 @@
         <v>0</v>
       </c>
       <c r="L164" t="n">
-        <v>55.99999999999991</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="M164" t="n">
-        <v>5.024039545778485e-14</v>
+        <v>6.45947941600091e-14</v>
       </c>
       <c r="N164" t="n">
-        <v>62.76500000000009</v>
+        <v>62.765</v>
       </c>
       <c r="O164" t="n">
-        <v>936.60101010101</v>
+        <v>936.6010101010102</v>
       </c>
       <c r="P164" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q164" t="n">
         <v>47.87888888888889</v>
@@ -11170,19 +11170,19 @@
         <v>0</v>
       </c>
       <c r="L165" t="n">
-        <v>55.49999999999992</v>
+        <v>55.5</v>
       </c>
       <c r="M165" t="n">
-        <v>-7.177199351112125e-15</v>
+        <v>2.870879740444848e-14</v>
       </c>
       <c r="N165" t="n">
-        <v>63.25500000000008</v>
+        <v>63.255</v>
       </c>
       <c r="O165" t="n">
-        <v>872.7070707070706</v>
+        <v>872.7070707070708</v>
       </c>
       <c r="P165" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q165" t="n">
         <v>47.87888888888889</v>
@@ -11235,19 +11235,19 @@
         <v>0</v>
       </c>
       <c r="L166" t="n">
-        <v>56.50000000000001</v>
+        <v>56.5</v>
       </c>
       <c r="M166" t="n">
-        <v>-7.105427357601002e-15</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
         <v>64.51400000000001</v>
       </c>
       <c r="O166" t="n">
-        <v>807.541414141414</v>
+        <v>807.5414141414142</v>
       </c>
       <c r="P166" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q166" t="n">
         <v>49.58333333333333</v>
@@ -11300,19 +11300,19 @@
         <v>0</v>
       </c>
       <c r="L167" t="n">
-        <v>61.49999999999999</v>
+        <v>61.5</v>
       </c>
       <c r="M167" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>49.77300000000005</v>
+        <v>49.77300000000003</v>
       </c>
       <c r="O167" t="n">
-        <v>757.2656565656564</v>
+        <v>757.2656565656566</v>
       </c>
       <c r="P167" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q167" t="n">
         <v>45.30555555555555</v>
@@ -11365,19 +11365,19 @@
         <v>0</v>
       </c>
       <c r="L168" t="n">
-        <v>56.99999999999999</v>
+        <v>57</v>
       </c>
       <c r="M168" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>0</v>
       </c>
       <c r="N168" t="n">
-        <v>54.18300000000004</v>
+        <v>54.18300000000003</v>
       </c>
       <c r="O168" t="n">
-        <v>702.5353535353534</v>
+        <v>702.5353535353536</v>
       </c>
       <c r="P168" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q168" t="n">
         <v>45.30555555555555</v>
@@ -11430,19 +11430,19 @@
         <v>0</v>
       </c>
       <c r="L169" t="n">
-        <v>50.49999999999999</v>
+        <v>50.5</v>
       </c>
       <c r="M169" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>0</v>
       </c>
       <c r="N169" t="n">
         <v>52.65499999999999</v>
       </c>
       <c r="O169" t="n">
-        <v>649.3484848484846</v>
+        <v>649.3484848484849</v>
       </c>
       <c r="P169" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q169" t="n">
         <v>38.49777777777778</v>
@@ -11483,10 +11483,10 @@
         <v>206.5</v>
       </c>
       <c r="H170" t="n">
-        <v>193.2027293133354</v>
+        <v>191.1621212121212</v>
       </c>
       <c r="I170" t="n">
-        <v>13.2972706866646</v>
+        <v>15.33787878787876</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -11498,13 +11498,13 @@
         <v>69.95</v>
       </c>
       <c r="M170" t="n">
-        <v>123.2527293133354</v>
+        <v>121.2121212121212</v>
       </c>
       <c r="N170" t="n">
         <v>3.552713678800501e-15</v>
       </c>
       <c r="O170" t="n">
-        <v>122.020202020202</v>
+        <v>120</v>
       </c>
       <c r="P170" t="n">
         <v>1</v>
@@ -11548,10 +11548,10 @@
         <v>228.5</v>
       </c>
       <c r="H171" t="n">
-        <v>68.9295918367347</v>
+        <v>70.97030405060713</v>
       </c>
       <c r="I171" t="n">
-        <v>159.5704081632653</v>
+        <v>157.5296959493929</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -11560,19 +11560,19 @@
         <v>0</v>
       </c>
       <c r="L171" t="n">
-        <v>68.9295918367347</v>
+        <v>69.95</v>
       </c>
       <c r="M171" t="n">
-        <v>0</v>
+        <v>1.020304050607123</v>
       </c>
       <c r="N171" t="n">
-        <v>1.000000000000004</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="O171" t="n">
-        <v>121.010101010101</v>
+        <v>121.0101010101011</v>
       </c>
       <c r="P171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q171" t="n">
         <v>39.29222222222222</v>
@@ -11613,7 +11613,7 @@
         <v>229.5</v>
       </c>
       <c r="H172" t="n">
-        <v>68.92959183673472</v>
+        <v>68.9295918367347</v>
       </c>
       <c r="I172" t="n">
         <v>160.5704081632653</v>
@@ -11625,13 +11625,13 @@
         <v>0</v>
       </c>
       <c r="L172" t="n">
-        <v>68.92959183673469</v>
+        <v>68.9295918367347</v>
       </c>
       <c r="M172" t="n">
-        <v>1.435439870222425e-14</v>
+        <v>-1.435439870222425e-14</v>
       </c>
       <c r="N172" t="n">
-        <v>1.000000000000018</v>
+        <v>1.000000000000004</v>
       </c>
       <c r="O172" t="n">
         <v>120</v>
@@ -11678,7 +11678,7 @@
         <v>200.5</v>
       </c>
       <c r="H173" t="n">
-        <v>70.880612244898</v>
+        <v>70.88061224489796</v>
       </c>
       <c r="I173" t="n">
         <v>129.619387755102</v>
@@ -11693,16 +11693,16 @@
         <v>69.88061224489796</v>
       </c>
       <c r="M173" t="n">
-        <v>1.000000000000043</v>
+        <v>1</v>
       </c>
       <c r="N173" t="n">
         <v>-3.552713678800501e-15</v>
       </c>
       <c r="O173" t="n">
-        <v>120.99</v>
+        <v>120.9900000000001</v>
       </c>
       <c r="P173" t="n">
-        <v>1</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="Q173" t="n">
         <v>42.30888888888889</v>
@@ -11764,7 +11764,7 @@
         <v>-3.552713678800501e-15</v>
       </c>
       <c r="O174" t="n">
-        <v>121.98</v>
+        <v>121.9800000000001</v>
       </c>
       <c r="P174" t="n">
         <v>1</v>
@@ -11829,7 +11829,7 @@
         <v>-3.552713678800501e-15</v>
       </c>
       <c r="O175" t="n">
-        <v>122.97</v>
+        <v>122.9700000000001</v>
       </c>
       <c r="P175" t="n">
         <v>1</v>
@@ -11894,7 +11894,7 @@
         <v>0.9999999999999929</v>
       </c>
       <c r="O176" t="n">
-        <v>121.959898989899</v>
+        <v>121.9598989898991</v>
       </c>
       <c r="P176" t="n">
         <v>-0</v>
@@ -11959,7 +11959,7 @@
         <v>7.105427357601002e-15</v>
       </c>
       <c r="O177" t="n">
-        <v>122.949898989899</v>
+        <v>122.9498989898991</v>
       </c>
       <c r="P177" t="n">
         <v>1</v>
@@ -12139,7 +12139,7 @@
         <v>266.5</v>
       </c>
       <c r="J180" t="n">
-        <v>275.144090669632</v>
+        <v>281.1437845784168</v>
       </c>
       <c r="K180" t="n">
         <v>0</v>
@@ -12148,13 +12148,13 @@
         <v>141.2326530612245</v>
       </c>
       <c r="M180" t="n">
-        <v>133.9114376084074</v>
+        <v>139.9111315171922</v>
       </c>
       <c r="N180" t="n">
         <v>7.105427357601002e-15</v>
       </c>
       <c r="O180" t="n">
-        <v>257.5022222222223</v>
+        <v>263.4419191919193</v>
       </c>
       <c r="P180" t="n">
         <v>1</v>
@@ -12219,7 +12219,7 @@
         <v>0</v>
       </c>
       <c r="O181" t="n">
-        <v>258.4922222222223</v>
+        <v>264.4319191919193</v>
       </c>
       <c r="P181" t="n">
         <v>1</v>
@@ -12263,13 +12263,13 @@
         <v>306</v>
       </c>
       <c r="H182" t="n">
-        <v>0</v>
+        <v>0.4797979797979792</v>
       </c>
       <c r="I182" t="n">
-        <v>306</v>
+        <v>305.520202020202</v>
       </c>
       <c r="J182" t="n">
-        <v>142.4457122242837</v>
+        <v>139.5365285508143</v>
       </c>
       <c r="K182" t="n">
         <v>0</v>
@@ -12278,13 +12278,13 @@
         <v>139.0163265306122</v>
       </c>
       <c r="M182" t="n">
-        <v>3.429385693671407</v>
+        <v>0.9999999999999949</v>
       </c>
       <c r="N182" t="n">
         <v>0</v>
       </c>
       <c r="O182" t="n">
-        <v>261.887314058957</v>
+        <v>265.4219191919193</v>
       </c>
       <c r="P182" t="n">
         <v>1</v>
@@ -12328,10 +12328,10 @@
         <v>293.5</v>
       </c>
       <c r="H183" t="n">
-        <v>5.52040816326533</v>
+        <v>3.499999999999993</v>
       </c>
       <c r="I183" t="n">
-        <v>287.9795918367347</v>
+        <v>290</v>
       </c>
       <c r="J183" t="n">
         <v>134.4959183673469</v>
@@ -12340,19 +12340,19 @@
         <v>0</v>
       </c>
       <c r="L183" t="n">
-        <v>139.0163265306122</v>
+        <v>137.9959183673469</v>
       </c>
       <c r="M183" t="n">
-        <v>0.9999999999999949</v>
+        <v>-1.435439870222425e-14</v>
       </c>
       <c r="N183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O183" t="n">
-        <v>262.877314058957</v>
+        <v>264.4118181818183</v>
       </c>
       <c r="P183" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="Q183" t="n">
         <v>63.23444444444444</v>
@@ -12393,13 +12393,13 @@
         <v>295</v>
       </c>
       <c r="H184" t="n">
-        <v>2.020408163265303</v>
+        <v>0</v>
       </c>
       <c r="I184" t="n">
-        <v>292.9795918367347</v>
+        <v>295</v>
       </c>
       <c r="J184" t="n">
-        <v>124.284693877551</v>
+        <v>253.9616718512663</v>
       </c>
       <c r="K184" t="n">
         <v>0</v>
@@ -12408,13 +12408,13 @@
         <v>125.3051020408163</v>
       </c>
       <c r="M184" t="n">
-        <v>1.000000000000009</v>
+        <v>128.65656981045</v>
       </c>
       <c r="N184" t="n">
         <v>0</v>
       </c>
       <c r="O184" t="n">
-        <v>263.867314058957</v>
+        <v>391.7818222941637</v>
       </c>
       <c r="P184" t="n">
         <v>1</v>
@@ -12464,22 +12464,22 @@
         <v>280</v>
       </c>
       <c r="J185" t="n">
-        <v>698.3102040816327</v>
+        <v>703.3102040816327</v>
       </c>
       <c r="K185" t="n">
         <v>0</v>
       </c>
       <c r="L185" t="n">
-        <v>143.3102040816327</v>
+        <v>143.3102040816326</v>
       </c>
       <c r="M185" t="n">
-        <v>555.0000000000001</v>
+        <v>560.0000000000001</v>
       </c>
       <c r="N185" t="n">
-        <v>-3.552713678800501e-14</v>
+        <v>-7.105427357601002e-15</v>
       </c>
       <c r="O185" t="n">
-        <v>813.3173140589571</v>
+        <v>946.1818222941638</v>
       </c>
       <c r="P185" t="n">
         <v>1</v>
@@ -12523,13 +12523,13 @@
         <v>222</v>
       </c>
       <c r="H186" t="n">
-        <v>51.98969231570175</v>
+        <v>38.5000000000001</v>
       </c>
       <c r="I186" t="n">
-        <v>170.0103076842983</v>
+        <v>183.4999999999999</v>
       </c>
       <c r="J186" t="n">
-        <v>90.3001036026656</v>
+        <v>103.7897959183673</v>
       </c>
       <c r="K186" t="n">
         <v>0</v>
@@ -12538,13 +12538,13 @@
         <v>142.2897959183673</v>
       </c>
       <c r="M186" t="n">
-        <v>-3.58859967555606e-14</v>
+        <v>-3.588599675556061e-14</v>
       </c>
       <c r="N186" t="n">
         <v>0.9999999999999929</v>
       </c>
       <c r="O186" t="n">
-        <v>812.3072130488561</v>
+        <v>945.1717212840628</v>
       </c>
       <c r="P186" t="n">
         <v>-0</v>
@@ -12588,13 +12588,13 @@
         <v>155.5</v>
       </c>
       <c r="H187" t="n">
-        <v>55.4795918367347</v>
+        <v>40.4592877861277</v>
       </c>
       <c r="I187" t="n">
-        <v>100.0204081632653</v>
+        <v>115.0407122138723</v>
       </c>
       <c r="J187" t="n">
-        <v>68.80918367346938</v>
+        <v>83.82948772407644</v>
       </c>
       <c r="K187" t="n">
         <v>0</v>
@@ -12609,7 +12609,7 @@
         <v>0.9999999999999929</v>
       </c>
       <c r="O187" t="n">
-        <v>811.2971120387551</v>
+        <v>944.1616202739618</v>
       </c>
       <c r="P187" t="n">
         <v>-0</v>
@@ -12653,10 +12653,10 @@
         <v>133</v>
       </c>
       <c r="H188" t="n">
-        <v>123.8129552586263</v>
+        <v>121.045918367347</v>
       </c>
       <c r="I188" t="n">
-        <v>9.187044741373711</v>
+        <v>11.95408163265301</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -12665,16 +12665,16 @@
         <v>0</v>
       </c>
       <c r="L188" t="n">
-        <v>120.0459183673469</v>
+        <v>120.045918367347</v>
       </c>
       <c r="M188" t="n">
-        <v>3.76703689127929</v>
+        <v>1.000000000000002</v>
       </c>
       <c r="N188" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>-7.105427357601002e-15</v>
       </c>
       <c r="O188" t="n">
-        <v>815.0264785611216</v>
+        <v>945.1516202739618</v>
       </c>
       <c r="P188" t="n">
         <v>1</v>
@@ -12721,7 +12721,7 @@
         <v>119.0255102040816</v>
       </c>
       <c r="I189" t="n">
-        <v>19.97448979591836</v>
+        <v>19.97448979591843</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -12733,16 +12733,16 @@
         <v>119.0255102040816</v>
       </c>
       <c r="M189" t="n">
-        <v>-2.153159805333637e-14</v>
+        <v>-2.153159805333638e-14</v>
       </c>
       <c r="N189" t="n">
         <v>0.9999999999999929</v>
       </c>
       <c r="O189" t="n">
-        <v>814.0163775510206</v>
+        <v>944.1415192638608</v>
       </c>
       <c r="P189" t="n">
-        <v>0</v>
+        <v>-1.891564011322376e-16</v>
       </c>
       <c r="Q189" t="n">
         <v>47.87888888888889</v>
@@ -12783,10 +12783,10 @@
         <v>150</v>
       </c>
       <c r="H190" t="n">
-        <v>150</v>
+        <v>134.0420955693841</v>
       </c>
       <c r="I190" t="n">
-        <v>0</v>
+        <v>15.95790443061594</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -12798,13 +12798,13 @@
         <v>122.330612244898</v>
       </c>
       <c r="M190" t="n">
-        <v>27.66938775510202</v>
+        <v>11.71148332448608</v>
       </c>
       <c r="N190" t="n">
         <v>-7.105427357601002e-15</v>
       </c>
       <c r="O190" t="n">
-        <v>841.4090714285716</v>
+        <v>955.735887755102</v>
       </c>
       <c r="P190" t="n">
         <v>1</v>
@@ -12863,13 +12863,13 @@
         <v>112.2887755102041</v>
       </c>
       <c r="M191" t="n">
-        <v>42.7112244897959</v>
+        <v>42.71122448979588</v>
       </c>
       <c r="N191" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>-7.105427357601002e-15</v>
       </c>
       <c r="O191" t="n">
-        <v>883.6931836734694</v>
+        <v>998.0199999999999</v>
       </c>
       <c r="P191" t="n">
         <v>1</v>
@@ -12913,10 +12913,10 @@
         <v>176</v>
       </c>
       <c r="H192" t="n">
-        <v>176</v>
+        <v>113.2887755102041</v>
       </c>
       <c r="I192" t="n">
-        <v>0</v>
+        <v>62.71122448979588</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -12928,13 +12928,13 @@
         <v>112.2887755102041</v>
       </c>
       <c r="M192" t="n">
-        <v>63.7112244897959</v>
+        <v>1.000000000000014</v>
       </c>
       <c r="N192" t="n">
         <v>7.105427357601002e-15</v>
       </c>
       <c r="O192" t="n">
-        <v>946.7672959183674</v>
+        <v>999.0099999999999</v>
       </c>
       <c r="P192" t="n">
         <v>1</v>
@@ -12978,10 +12978,10 @@
         <v>158</v>
       </c>
       <c r="H193" t="n">
-        <v>158</v>
+        <v>105.2295918367347</v>
       </c>
       <c r="I193" t="n">
-        <v>0</v>
+        <v>52.77040816326533</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -12993,7 +12993,7 @@
         <v>104.2295918367347</v>
       </c>
       <c r="M193" t="n">
-        <v>53.77040816326532</v>
+        <v>0.9999999999999858</v>
       </c>
       <c r="N193" t="n">
         <v>7.105427357601002e-15</v>
@@ -13693,13 +13693,13 @@
         <v>27</v>
       </c>
       <c r="H204" t="n">
-        <v>27</v>
+        <v>22.73543308804642</v>
       </c>
       <c r="I204" t="n">
-        <v>0</v>
+        <v>4.26456691195358</v>
       </c>
       <c r="J204" t="n">
-        <v>275.144090669632</v>
+        <v>281.1437845784168</v>
       </c>
       <c r="K204" t="n">
         <v>0</v>
@@ -13708,13 +13708,13 @@
         <v>141.2326530612245</v>
       </c>
       <c r="M204" t="n">
-        <v>160.9114376084074</v>
+        <v>162.6465646052386</v>
       </c>
       <c r="N204" t="n">
         <v>7.105427357601002e-15</v>
       </c>
       <c r="O204" t="n">
-        <v>279.3023232323233</v>
+        <v>281.0200989591862</v>
       </c>
       <c r="P204" t="n">
         <v>1</v>
@@ -13770,16 +13770,16 @@
         <v>0</v>
       </c>
       <c r="L205" t="n">
-        <v>29.49999999999999</v>
+        <v>29.5</v>
       </c>
       <c r="M205" t="n">
-        <v>-1.076579902666819e-14</v>
+        <v>6.100619448445305e-14</v>
       </c>
       <c r="N205" t="n">
         <v>110.177</v>
       </c>
       <c r="O205" t="n">
-        <v>168.0124242424243</v>
+        <v>169.7301999692873</v>
       </c>
       <c r="P205" t="n">
         <v>0</v>
@@ -13829,7 +13829,7 @@
         <v>0</v>
       </c>
       <c r="J206" t="n">
-        <v>142.4457122242837</v>
+        <v>139.5365285508143</v>
       </c>
       <c r="K206" t="n">
         <v>0</v>
@@ -13838,13 +13838,13 @@
         <v>139.0163265306122</v>
       </c>
       <c r="M206" t="n">
-        <v>34.92938569367141</v>
+        <v>32.02020202020199</v>
       </c>
       <c r="N206" t="n">
         <v>0</v>
       </c>
       <c r="O206" t="n">
-        <v>202.592516079159</v>
+        <v>201.4301999692873</v>
       </c>
       <c r="P206" t="n">
         <v>1</v>
@@ -13903,13 +13903,13 @@
         <v>139.0163265306122</v>
       </c>
       <c r="M207" t="n">
-        <v>31.47959183673467</v>
+        <v>31.47959183673469</v>
       </c>
       <c r="N207" t="n">
         <v>0</v>
       </c>
       <c r="O207" t="n">
-        <v>233.7573119975263</v>
+        <v>232.5949958876546</v>
       </c>
       <c r="P207" t="n">
         <v>1</v>
@@ -13959,7 +13959,7 @@
         <v>0</v>
       </c>
       <c r="J208" t="n">
-        <v>124.284693877551</v>
+        <v>253.9616718512663</v>
       </c>
       <c r="K208" t="n">
         <v>0</v>
@@ -13968,13 +13968,13 @@
         <v>125.3051020408163</v>
       </c>
       <c r="M208" t="n">
-        <v>45.47959183673469</v>
+        <v>175.15656981045</v>
       </c>
       <c r="N208" t="n">
         <v>0</v>
       </c>
       <c r="O208" t="n">
-        <v>278.7821079158937</v>
+        <v>406.0000000000001</v>
       </c>
       <c r="P208" t="n">
         <v>1</v>
@@ -14018,13 +14018,13 @@
         <v>45</v>
       </c>
       <c r="H209" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I209" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J209" t="n">
-        <v>698.3102040816327</v>
+        <v>703.3102040816327</v>
       </c>
       <c r="K209" t="n">
         <v>0</v>
@@ -14039,7 +14039,7 @@
         <v>-7.105427357601002e-15</v>
       </c>
       <c r="O209" t="n">
-        <v>872.7821079158937</v>
+        <v>1000</v>
       </c>
       <c r="P209" t="n">
         <v>1</v>
@@ -14089,22 +14089,22 @@
         <v>0</v>
       </c>
       <c r="J210" t="n">
-        <v>90.3001036026656</v>
+        <v>103.7897959183673</v>
       </c>
       <c r="K210" t="n">
         <v>0</v>
       </c>
       <c r="L210" t="n">
-        <v>128.8001036026656</v>
+        <v>142.2897959183673</v>
       </c>
       <c r="M210" t="n">
-        <v>-1.220123889689061e-13</v>
+        <v>-7.177199351112125e-15</v>
       </c>
       <c r="N210" t="n">
-        <v>14.21989846938768</v>
+        <v>1.000000000000021</v>
       </c>
       <c r="O210" t="n">
-        <v>858.4185741084312</v>
+        <v>998.989898989899</v>
       </c>
       <c r="P210" t="n">
         <v>0</v>
@@ -14154,25 +14154,25 @@
         <v>0</v>
       </c>
       <c r="J211" t="n">
-        <v>68.80918367346938</v>
+        <v>83.82948772407644</v>
       </c>
       <c r="K211" t="n">
         <v>0</v>
       </c>
       <c r="L211" t="n">
-        <v>111.3091836734693</v>
+        <v>125.3091836734694</v>
       </c>
       <c r="M211" t="n">
-        <v>-1.435439870222425e-14</v>
+        <v>1.02030405060711</v>
       </c>
       <c r="N211" t="n">
-        <v>13.72000000000003</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="O211" t="n">
-        <v>844.5599882498453</v>
+        <v>1000</v>
       </c>
       <c r="P211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q211" t="n">
         <v>54.18555555555556</v>
@@ -14228,16 +14228,16 @@
         <v>50.5</v>
       </c>
       <c r="M212" t="n">
-        <v>-5.024039545778486e-14</v>
+        <v>6.45947941600091e-14</v>
       </c>
       <c r="N212" t="n">
         <v>68.155</v>
       </c>
       <c r="O212" t="n">
-        <v>775.7165539064109</v>
+        <v>931.1565656565657</v>
       </c>
       <c r="P212" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q212" t="n">
         <v>47.87888888888889</v>
@@ -14290,19 +14290,19 @@
         <v>0</v>
       </c>
       <c r="L213" t="n">
-        <v>35.00000000000003</v>
+        <v>35</v>
       </c>
       <c r="M213" t="n">
-        <v>-3.588599675556061e-14</v>
+        <v>-7.177199351112125e-15</v>
       </c>
       <c r="N213" t="n">
-        <v>83.34499999999997</v>
+        <v>83.345</v>
       </c>
       <c r="O213" t="n">
-        <v>691.5296852195422</v>
+        <v>846.969696969697</v>
       </c>
       <c r="P213" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q213" t="n">
         <v>47.87888888888889</v>
@@ -14355,19 +14355,19 @@
         <v>0</v>
       </c>
       <c r="L214" t="n">
-        <v>13.50000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="M214" t="n">
-        <v>-8.881784197001252e-15</v>
+        <v>0</v>
       </c>
       <c r="N214" t="n">
         <v>106.654</v>
       </c>
       <c r="O214" t="n">
-        <v>583.798372088229</v>
+        <v>739.2383838383838</v>
       </c>
       <c r="P214" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q214" t="n">
         <v>49.58333333333333</v>
@@ -14420,19 +14420,19 @@
         <v>0</v>
       </c>
       <c r="L215" t="n">
-        <v>6.499999999999997</v>
+        <v>6.5</v>
       </c>
       <c r="M215" t="n">
-        <v>2.664535259100376e-15</v>
+        <v>0</v>
       </c>
       <c r="N215" t="n">
         <v>103.673</v>
       </c>
       <c r="O215" t="n">
-        <v>479.078170068027</v>
+        <v>634.5181818181818</v>
       </c>
       <c r="P215" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q215" t="n">
         <v>45.30555555555555</v>
@@ -14485,19 +14485,19 @@
         <v>0</v>
       </c>
       <c r="L216" t="n">
-        <v>5.000000000000001</v>
+        <v>5</v>
       </c>
       <c r="M216" t="n">
-        <v>-8.881784197001252e-16</v>
+        <v>0</v>
       </c>
       <c r="N216" t="n">
         <v>105.143</v>
       </c>
       <c r="O216" t="n">
-        <v>372.8731195629764</v>
+        <v>528.3131313131313</v>
       </c>
       <c r="P216" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q216" t="n">
         <v>45.30555555555555</v>
@@ -14550,19 +14550,19 @@
         <v>0</v>
       </c>
       <c r="L217" t="n">
-        <v>4.499999999999998</v>
+        <v>4.500000000000001</v>
       </c>
       <c r="M217" t="n">
-        <v>1.77635683940025e-15</v>
+        <v>-8.881784197001252e-16</v>
       </c>
       <c r="N217" t="n">
         <v>97.73499999999999</v>
       </c>
       <c r="O217" t="n">
-        <v>274.1508973407542</v>
+        <v>429.5909090909091</v>
       </c>
       <c r="P217" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q217" t="n">
         <v>38.49777777777778</v>
@@ -15259,7 +15259,7 @@
         <v>0</v>
       </c>
       <c r="J228" t="n">
-        <v>275.144090669632</v>
+        <v>281.1437845784168</v>
       </c>
       <c r="K228" t="n">
         <v>0</v>
@@ -15268,16 +15268,16 @@
         <v>141.2326530612245</v>
       </c>
       <c r="M228" t="n">
-        <v>133.9114376084075</v>
+        <v>139.9111315171923</v>
       </c>
       <c r="N228" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>3.552713678800501e-14</v>
       </c>
       <c r="O228" t="n">
-        <v>252.5723232323234</v>
+        <v>258.5120202020204</v>
       </c>
       <c r="P228" t="n">
-        <v>1</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="Q228" t="n">
         <v>50.42555555555555</v>
@@ -15327,22 +15327,22 @@
         <v>0</v>
       </c>
       <c r="K229" t="n">
-        <v>7.500408163265138</v>
+        <v>1.500102040816157</v>
       </c>
       <c r="L229" t="n">
-        <v>8.000408163265208</v>
+        <v>2.000102040816106</v>
       </c>
       <c r="M229" t="n">
-        <v>-6.728624391667615e-14</v>
+        <v>5.696901984945248e-14</v>
       </c>
       <c r="N229" t="n">
-        <v>131.2466000000001</v>
+        <v>137.1269000000002</v>
       </c>
       <c r="O229" t="n">
         <v>120</v>
       </c>
       <c r="P229" t="n">
-        <v>0</v>
+        <v>8.43769498715119e-17</v>
       </c>
       <c r="Q229" t="n">
         <v>55</v>
@@ -15389,7 +15389,7 @@
         <v>0</v>
       </c>
       <c r="J230" t="n">
-        <v>142.4457122242837</v>
+        <v>139.5365285508143</v>
       </c>
       <c r="K230" t="n">
         <v>0</v>
@@ -15398,13 +15398,13 @@
         <v>139.0163265306122</v>
       </c>
       <c r="M230" t="n">
-        <v>9.92938569367141</v>
+        <v>7.020202020202008</v>
       </c>
       <c r="N230" t="n">
         <v>0</v>
       </c>
       <c r="O230" t="n">
-        <v>129.8300918367347</v>
+        <v>126.95</v>
       </c>
       <c r="P230" t="n">
         <v>1</v>
@@ -15463,13 +15463,13 @@
         <v>139.0163265306122</v>
       </c>
       <c r="M231" t="n">
-        <v>19.47959183673467</v>
+        <v>19.47959183673468</v>
       </c>
       <c r="N231" t="n">
         <v>0</v>
       </c>
       <c r="O231" t="n">
-        <v>149.114887755102</v>
+        <v>146.2347959183674</v>
       </c>
       <c r="P231" t="n">
         <v>1</v>
@@ -15519,7 +15519,7 @@
         <v>0</v>
       </c>
       <c r="J232" t="n">
-        <v>124.284693877551</v>
+        <v>253.9616718512663</v>
       </c>
       <c r="K232" t="n">
         <v>0</v>
@@ -15528,13 +15528,13 @@
         <v>125.3051020408163</v>
       </c>
       <c r="M232" t="n">
-        <v>31.47959183673468</v>
+        <v>161.1565698104499</v>
       </c>
       <c r="N232" t="n">
         <v>0</v>
       </c>
       <c r="O232" t="n">
-        <v>180.2796836734694</v>
+        <v>305.7798000307127</v>
       </c>
       <c r="P232" t="n">
         <v>1</v>
@@ -15584,7 +15584,7 @@
         <v>0</v>
       </c>
       <c r="J233" t="n">
-        <v>698.3102040816327</v>
+        <v>703.3102040816327</v>
       </c>
       <c r="K233" t="n">
         <v>0</v>
@@ -15593,13 +15593,13 @@
         <v>143.3102040816326</v>
       </c>
       <c r="M233" t="n">
-        <v>595.0000000000001</v>
+        <v>600</v>
       </c>
       <c r="N233" t="n">
         <v>-7.105427357601002e-15</v>
       </c>
       <c r="O233" t="n">
-        <v>769.3296836734695</v>
+        <v>899.7798000307127</v>
       </c>
       <c r="P233" t="n">
         <v>1</v>
@@ -15649,25 +15649,25 @@
         <v>0</v>
       </c>
       <c r="J234" t="n">
-        <v>90.3001036026656</v>
+        <v>103.7897959183673</v>
       </c>
       <c r="K234" t="n">
         <v>0</v>
       </c>
       <c r="L234" t="n">
-        <v>139.8001036026656</v>
+        <v>143.3102040816326</v>
       </c>
       <c r="M234" t="n">
-        <v>-9.33035915644576e-14</v>
+        <v>9.979591836734704</v>
       </c>
       <c r="N234" t="n">
-        <v>3.439898469387678</v>
+        <v>-7.105427357601002e-15</v>
       </c>
       <c r="O234" t="n">
-        <v>765.855038754896</v>
+        <v>909.6595959490801</v>
       </c>
       <c r="P234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q234" t="n">
         <v>46.18888888888889</v>
@@ -15714,7 +15714,7 @@
         <v>0</v>
       </c>
       <c r="J235" t="n">
-        <v>68.80918367346938</v>
+        <v>83.82948772407644</v>
       </c>
       <c r="K235" t="n">
         <v>0</v>
@@ -15723,13 +15723,13 @@
         <v>125.3091836734694</v>
       </c>
       <c r="M235" t="n">
-        <v>4.500000000000156</v>
+        <v>19.52030405060705</v>
       </c>
       <c r="N235" t="n">
         <v>7.105427357601002e-15</v>
       </c>
       <c r="O235" t="n">
-        <v>770.3100387548961</v>
+        <v>928.9846969591811</v>
       </c>
       <c r="P235" t="n">
         <v>1</v>
@@ -15788,16 +15788,16 @@
         <v>64</v>
       </c>
       <c r="M236" t="n">
-        <v>-4.306319610667274e-14</v>
+        <v>7.177199351112123e-14</v>
       </c>
       <c r="N236" t="n">
         <v>54.925</v>
       </c>
       <c r="O236" t="n">
-        <v>714.8302407750981</v>
+        <v>873.5048989793831</v>
       </c>
       <c r="P236" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q236" t="n">
         <v>47.87888888888889</v>
@@ -15850,19 +15850,19 @@
         <v>0</v>
       </c>
       <c r="L237" t="n">
-        <v>41.00000000000005</v>
+        <v>41.00000000000001</v>
       </c>
       <c r="M237" t="n">
-        <v>0</v>
+        <v>4.306319610667274e-14</v>
       </c>
       <c r="N237" t="n">
-        <v>77.46499999999995</v>
+        <v>77.465</v>
       </c>
       <c r="O237" t="n">
-        <v>636.5827660276234</v>
+        <v>795.2574242319084</v>
       </c>
       <c r="P237" t="n">
-        <v>0</v>
+        <v>1.826264541714099e-16</v>
       </c>
       <c r="Q237" t="n">
         <v>47.87888888888889</v>
@@ -15915,19 +15915,19 @@
         <v>0</v>
       </c>
       <c r="L238" t="n">
-        <v>13.50000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="M238" t="n">
-        <v>-8.881784197001252e-15</v>
+        <v>0</v>
       </c>
       <c r="N238" t="n">
         <v>106.654</v>
       </c>
       <c r="O238" t="n">
-        <v>528.8514528963102</v>
+        <v>687.5261111005952</v>
       </c>
       <c r="P238" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q238" t="n">
         <v>49.58333333333333</v>
@@ -15980,19 +15980,19 @@
         <v>0</v>
       </c>
       <c r="L239" t="n">
-        <v>8.499999999999993</v>
+        <v>8.5</v>
       </c>
       <c r="M239" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>0</v>
       </c>
       <c r="N239" t="n">
         <v>101.713</v>
       </c>
       <c r="O239" t="n">
-        <v>426.1110488559061</v>
+        <v>584.7857070601912</v>
       </c>
       <c r="P239" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q239" t="n">
         <v>45.30555555555555</v>
@@ -16045,19 +16045,19 @@
         <v>0</v>
       </c>
       <c r="L240" t="n">
-        <v>7.499999999999995</v>
+        <v>7.5</v>
       </c>
       <c r="M240" t="n">
-        <v>5.329070518200751e-15</v>
+        <v>0</v>
       </c>
       <c r="N240" t="n">
         <v>102.693</v>
       </c>
       <c r="O240" t="n">
-        <v>322.3807458256031</v>
+        <v>481.0554040298881</v>
       </c>
       <c r="P240" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q240" t="n">
         <v>45.30555555555555</v>
@@ -16110,19 +16110,19 @@
         <v>0</v>
       </c>
       <c r="L241" t="n">
-        <v>6.499999999999997</v>
+        <v>6.499999999999999</v>
       </c>
       <c r="M241" t="n">
-        <v>2.664535259100376e-15</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="N241" t="n">
         <v>95.77499999999999</v>
       </c>
       <c r="O241" t="n">
-        <v>225.6383215831788</v>
+        <v>384.3129797874639</v>
       </c>
       <c r="P241" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q241" t="n">
         <v>38.49777777777778</v>
@@ -16151,7 +16151,7 @@
         <v>1</v>
       </c>
       <c r="D242" t="n">
-        <v>67.804</v>
+        <v>68.551</v>
       </c>
       <c r="E242" t="n">
         <v>35.363</v>
@@ -16172,10 +16172,10 @@
         <v>0</v>
       </c>
       <c r="K242" t="n">
-        <v>177.399876314162</v>
+        <v>178.1621212121212</v>
       </c>
       <c r="L242" t="n">
-        <v>69.18775510204082</v>
+        <v>69.95</v>
       </c>
       <c r="M242" t="n">
         <v>121.2121212121212</v>
@@ -16216,7 +16216,7 @@
         <v>2</v>
       </c>
       <c r="D243" t="n">
-        <v>67.804</v>
+        <v>68.551</v>
       </c>
       <c r="E243" t="n">
         <v>35.363</v>
@@ -16237,10 +16237,10 @@
         <v>0</v>
       </c>
       <c r="K243" t="n">
-        <v>57.70805915264791</v>
+        <v>58.47030405060709</v>
       </c>
       <c r="L243" t="n">
-        <v>69.18775510204082</v>
+        <v>69.95</v>
       </c>
       <c r="M243" t="n">
         <v>1.020304050607088</v>
@@ -16281,7 +16281,7 @@
         <v>3</v>
       </c>
       <c r="D244" t="n">
-        <v>67.804</v>
+        <v>68.551</v>
       </c>
       <c r="E244" t="n">
         <v>35.363</v>
@@ -16302,16 +16302,16 @@
         <v>0</v>
       </c>
       <c r="K244" t="n">
-        <v>55.16734693877552</v>
+        <v>55.9295918367347</v>
       </c>
       <c r="L244" t="n">
-        <v>68.16734693877552</v>
+        <v>68.9295918367347</v>
       </c>
       <c r="M244" t="n">
-        <v>-7.105427357601002e-15</v>
+        <v>0</v>
       </c>
       <c r="N244" t="n">
-        <v>0.9999999999999893</v>
+        <v>1.000000000000004</v>
       </c>
       <c r="O244" t="n">
         <v>120</v>
@@ -16346,7 +16346,7 @@
         <v>4</v>
       </c>
       <c r="D245" t="n">
-        <v>67.804</v>
+        <v>68.483</v>
       </c>
       <c r="E245" t="n">
         <v>38.078</v>
@@ -16367,16 +16367,16 @@
         <v>0</v>
       </c>
       <c r="K245" t="n">
-        <v>53.1877551020408</v>
+        <v>53.88061224489795</v>
       </c>
       <c r="L245" t="n">
-        <v>69.18775510204081</v>
+        <v>69.88061224489796</v>
       </c>
       <c r="M245" t="n">
         <v>0.9999999999999929</v>
       </c>
       <c r="N245" t="n">
-        <v>1.06581410364015e-14</v>
+        <v>-3.552713678800501e-15</v>
       </c>
       <c r="O245" t="n">
         <v>120.99</v>
@@ -16411,7 +16411,7 @@
         <v>5</v>
       </c>
       <c r="D246" t="n">
-        <v>67.804</v>
+        <v>68.483</v>
       </c>
       <c r="E246" t="n">
         <v>38.078</v>
@@ -16432,19 +16432,19 @@
         <v>0</v>
       </c>
       <c r="K246" t="n">
-        <v>261.1199048826754</v>
+        <v>273.1248730346132</v>
       </c>
       <c r="L246" t="n">
-        <v>69.18775510204081</v>
+        <v>69.88061224489796</v>
       </c>
       <c r="M246" t="n">
-        <v>213.9321497806346</v>
+        <v>225.2442607897153</v>
       </c>
       <c r="N246" t="n">
-        <v>1.06581410364015e-14</v>
+        <v>-3.552713678800501e-15</v>
       </c>
       <c r="O246" t="n">
-        <v>332.7828282828283</v>
+        <v>343.9818181818181</v>
       </c>
       <c r="P246" t="n">
         <v>1</v>
@@ -16476,7 +16476,7 @@
         <v>6</v>
       </c>
       <c r="D247" t="n">
-        <v>75.039</v>
+        <v>75.066</v>
       </c>
       <c r="E247" t="n">
         <v>38.078</v>
@@ -16506,10 +16506,10 @@
         <v>0</v>
       </c>
       <c r="N247" t="n">
-        <v>59.35899999999999</v>
+        <v>59.386</v>
       </c>
       <c r="O247" t="n">
-        <v>272.8242424242424</v>
+        <v>283.9959595959596</v>
       </c>
       <c r="P247" t="n">
         <v>0</v>
@@ -16541,7 +16541,7 @@
         <v>7</v>
       </c>
       <c r="D248" t="n">
-        <v>78.58799999999999</v>
+        <v>84.11799999999999</v>
       </c>
       <c r="E248" t="n">
         <v>48.821</v>
@@ -16571,10 +16571,10 @@
         <v>0</v>
       </c>
       <c r="N248" t="n">
-        <v>73.68799999999999</v>
+        <v>79.21799999999999</v>
       </c>
       <c r="O248" t="n">
-        <v>198.3919191919192</v>
+        <v>203.9777777777778</v>
       </c>
       <c r="P248" t="n">
         <v>0</v>
@@ -16606,7 +16606,7 @@
         <v>8</v>
       </c>
       <c r="D249" t="n">
-        <v>78.58799999999999</v>
+        <v>84.11799999999999</v>
       </c>
       <c r="E249" t="n">
         <v>48.821</v>
@@ -16636,7 +16636,7 @@
         <v>0</v>
       </c>
       <c r="N249" t="n">
-        <v>77.60799999999999</v>
+        <v>83.13799999999999</v>
       </c>
       <c r="O249" t="n">
         <v>120</v>
@@ -16671,7 +16671,7 @@
         <v>9</v>
       </c>
       <c r="D250" t="n">
-        <v>118.618</v>
+        <v>125.853</v>
       </c>
       <c r="E250" t="n">
         <v>61.411</v>
@@ -16692,13 +16692,13 @@
         <v>0</v>
       </c>
       <c r="K250" t="n">
-        <v>121.5590795608112</v>
+        <v>128.9417326220356</v>
       </c>
       <c r="L250" t="n">
-        <v>121.0387755102041</v>
+        <v>128.4214285714285</v>
       </c>
       <c r="M250" t="n">
-        <v>1.020304050607095</v>
+        <v>1.020304050607081</v>
       </c>
       <c r="N250" t="n">
         <v>0</v>
@@ -16736,7 +16736,7 @@
         <v>10</v>
       </c>
       <c r="D251" t="n">
-        <v>116.928</v>
+        <v>138.408</v>
       </c>
       <c r="E251" t="n">
         <v>45.383</v>
@@ -16757,16 +16757,16 @@
         <v>-0</v>
       </c>
       <c r="K251" t="n">
-        <v>117.2938775510204</v>
+        <v>139.2122448979592</v>
       </c>
       <c r="L251" t="n">
-        <v>118.2938775510204</v>
+        <v>140.2122448979592</v>
       </c>
       <c r="M251" t="n">
-        <v>-7.177199351112124e-15</v>
+        <v>-2.153159805333638e-14</v>
       </c>
       <c r="N251" t="n">
-        <v>0.9999999999999929</v>
+        <v>0.9999999999999787</v>
       </c>
       <c r="O251" t="n">
         <v>120</v>
@@ -16801,7 +16801,7 @@
         <v>11</v>
       </c>
       <c r="D252" t="n">
-        <v>116.928</v>
+        <v>138.408</v>
       </c>
       <c r="E252" t="n">
         <v>45.383</v>
@@ -16819,22 +16819,22 @@
         <v>2</v>
       </c>
       <c r="J252" t="n">
-        <v>275.144090669632</v>
+        <v>281.1437845784168</v>
       </c>
       <c r="K252" t="n">
         <v>0</v>
       </c>
       <c r="L252" t="n">
-        <v>119.3142857142857</v>
+        <v>141.2326530612245</v>
       </c>
       <c r="M252" t="n">
-        <v>155.8298049553462</v>
+        <v>139.9111315171922</v>
       </c>
       <c r="N252" t="n">
         <v>7.105427357601002e-15</v>
       </c>
       <c r="O252" t="n">
-        <v>274.2715069057927</v>
+        <v>258.5120202020203</v>
       </c>
       <c r="P252" t="n">
         <v>1</v>
@@ -16866,7 +16866,7 @@
         <v>12</v>
       </c>
       <c r="D253" t="n">
-        <v>115.137</v>
+        <v>139.087</v>
       </c>
       <c r="E253" t="n">
         <v>49.5</v>
@@ -16893,13 +16893,13 @@
         <v>7.5</v>
       </c>
       <c r="M253" t="n">
-        <v>-1.704584845889129e-14</v>
+        <v>1.16629489455572e-14</v>
       </c>
       <c r="N253" t="n">
-        <v>107.787</v>
+        <v>131.737</v>
       </c>
       <c r="O253" t="n">
-        <v>165.3957493300351</v>
+        <v>125.4443434343435</v>
       </c>
       <c r="P253" t="n">
         <v>0</v>
@@ -16931,7 +16931,7 @@
         <v>13</v>
       </c>
       <c r="D254" t="n">
-        <v>112.44</v>
+        <v>136.236</v>
       </c>
       <c r="E254" t="n">
         <v>56.911</v>
@@ -16943,28 +16943,28 @@
         <v>33.5</v>
       </c>
       <c r="H254" t="n">
-        <v>0</v>
+        <v>0.4797979797979792</v>
       </c>
       <c r="I254" t="n">
-        <v>33.5</v>
+        <v>33.02020202020202</v>
       </c>
       <c r="J254" t="n">
-        <v>142.4457122242837</v>
+        <v>139.5365285508143</v>
       </c>
       <c r="K254" t="n">
         <v>0</v>
       </c>
       <c r="L254" t="n">
-        <v>114.734693877551</v>
+        <v>139.0163265306122</v>
       </c>
       <c r="M254" t="n">
-        <v>27.71101834673265</v>
+        <v>0.9999999999999805</v>
       </c>
       <c r="N254" t="n">
         <v>0</v>
       </c>
       <c r="O254" t="n">
-        <v>192.8296574933004</v>
+        <v>126.4343434343435</v>
       </c>
       <c r="P254" t="n">
         <v>1</v>
@@ -16996,7 +16996,7 @@
         <v>14</v>
       </c>
       <c r="D255" t="n">
-        <v>112.44</v>
+        <v>136.236</v>
       </c>
       <c r="E255" t="n">
         <v>56.911</v>
@@ -17008,10 +17008,10 @@
         <v>46</v>
       </c>
       <c r="H255" t="n">
-        <v>22.80612774815458</v>
+        <v>46</v>
       </c>
       <c r="I255" t="n">
-        <v>23.19387225184542</v>
+        <v>0</v>
       </c>
       <c r="J255" t="n">
         <v>134.4959183673469</v>
@@ -17020,16 +17020,16 @@
         <v>0</v>
       </c>
       <c r="L255" t="n">
-        <v>114.734693877551</v>
+        <v>139.0163265306122</v>
       </c>
       <c r="M255" t="n">
-        <v>42.56735223795048</v>
+        <v>41.47959183673468</v>
       </c>
       <c r="N255" t="n">
         <v>0</v>
       </c>
       <c r="O255" t="n">
-        <v>234.9713362088714</v>
+        <v>167.4991393527108</v>
       </c>
       <c r="P255" t="n">
         <v>1</v>
@@ -17061,7 +17061,7 @@
         <v>15</v>
       </c>
       <c r="D256" t="n">
-        <v>114.258</v>
+        <v>122.799</v>
       </c>
       <c r="E256" t="n">
         <v>53.581</v>
@@ -17073,28 +17073,28 @@
         <v>60</v>
       </c>
       <c r="H256" t="n">
-        <v>60</v>
+        <v>16.75349455199543</v>
       </c>
       <c r="I256" t="n">
-        <v>0</v>
+        <v>43.24650544800457</v>
       </c>
       <c r="J256" t="n">
-        <v>124.284693877551</v>
+        <v>253.9616718512663</v>
       </c>
       <c r="K256" t="n">
         <v>0</v>
       </c>
       <c r="L256" t="n">
-        <v>116.5897959183673</v>
+        <v>125.3051020408163</v>
       </c>
       <c r="M256" t="n">
-        <v>67.69489795918371</v>
+        <v>145.4100643624453</v>
       </c>
       <c r="N256" t="n">
         <v>0</v>
       </c>
       <c r="O256" t="n">
-        <v>301.9892851884633</v>
+        <v>311.4551030715317</v>
       </c>
       <c r="P256" t="n">
         <v>1</v>
@@ -17126,7 +17126,7 @@
         <v>16</v>
       </c>
       <c r="D257" t="n">
-        <v>131.363</v>
+        <v>140.444</v>
       </c>
       <c r="E257" t="n">
         <v>41.57</v>
@@ -17138,28 +17138,28 @@
         <v>77.5</v>
       </c>
       <c r="H257" t="n">
-        <v>35.73367346938767</v>
+        <v>39.99999999999989</v>
       </c>
       <c r="I257" t="n">
-        <v>41.76632653061233</v>
+        <v>37.50000000000011</v>
       </c>
       <c r="J257" t="n">
-        <v>698.3102040816327</v>
+        <v>703.3102040816327</v>
       </c>
       <c r="K257" t="n">
         <v>0</v>
       </c>
       <c r="L257" t="n">
-        <v>134.0438775510204</v>
+        <v>143.3102040816326</v>
       </c>
       <c r="M257" t="n">
         <v>600</v>
       </c>
       <c r="N257" t="n">
-        <v>2.131628207280301e-14</v>
+        <v>-7.105427357601002e-15</v>
       </c>
       <c r="O257" t="n">
-        <v>895.9892851884632</v>
+        <v>905.4551030715317</v>
       </c>
       <c r="P257" t="n">
         <v>1</v>
@@ -17191,7 +17191,7 @@
         <v>17</v>
       </c>
       <c r="D258" t="n">
-        <v>131.363</v>
+        <v>140.444</v>
       </c>
       <c r="E258" t="n">
         <v>41.57</v>
@@ -17209,22 +17209,22 @@
         <v>0</v>
       </c>
       <c r="J258" t="n">
-        <v>90.3001036026656</v>
+        <v>103.7897959183673</v>
       </c>
       <c r="K258" t="n">
         <v>0</v>
       </c>
       <c r="L258" t="n">
-        <v>134.0438775510204</v>
+        <v>143.3102040816326</v>
       </c>
       <c r="M258" t="n">
-        <v>46.25622605164514</v>
+        <v>50.47959183673473</v>
       </c>
       <c r="N258" t="n">
-        <v>2.131628207280301e-14</v>
+        <v>-7.105427357601002e-15</v>
       </c>
       <c r="O258" t="n">
-        <v>941.7829489795919</v>
+        <v>955.429898989899</v>
       </c>
       <c r="P258" t="n">
         <v>1</v>
@@ -17256,7 +17256,7 @@
         <v>18</v>
       </c>
       <c r="D259" t="n">
-        <v>94.574</v>
+        <v>122.803</v>
       </c>
       <c r="E259" t="n">
         <v>48.767</v>
@@ -17274,19 +17274,19 @@
         <v>0</v>
       </c>
       <c r="J259" t="n">
-        <v>68.80918367346938</v>
+        <v>83.82948772407644</v>
       </c>
       <c r="K259" t="n">
         <v>0</v>
       </c>
       <c r="L259" t="n">
-        <v>96.50408163265307</v>
+        <v>125.3091836734694</v>
       </c>
       <c r="M259" t="n">
-        <v>58.8051020408163</v>
+        <v>45.02030405060705</v>
       </c>
       <c r="N259" t="n">
-        <v>-7.105427357601002e-15</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="O259" t="n">
         <v>1000</v>
@@ -17321,7 +17321,7 @@
         <v>19</v>
       </c>
       <c r="D260" t="n">
-        <v>91.65600000000001</v>
+        <v>117.645</v>
       </c>
       <c r="E260" t="n">
         <v>43.091</v>
@@ -17345,19 +17345,19 @@
         <v>0</v>
       </c>
       <c r="L260" t="n">
-        <v>64.49999999999997</v>
+        <v>64.5</v>
       </c>
       <c r="M260" t="n">
-        <v>1.435439870222425e-13</v>
+        <v>1.14835189617794e-13</v>
       </c>
       <c r="N260" t="n">
-        <v>28.44600000000004</v>
+        <v>54.435</v>
       </c>
       <c r="O260" t="n">
-        <v>971.2666666666668</v>
+        <v>945.0151515151516</v>
       </c>
       <c r="P260" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q260" t="n">
         <v>47.87888888888889</v>
@@ -17386,7 +17386,7 @@
         <v>20</v>
       </c>
       <c r="D261" t="n">
-        <v>91.65600000000001</v>
+        <v>117.645</v>
       </c>
       <c r="E261" t="n">
         <v>43.091</v>
@@ -17410,19 +17410,19 @@
         <v>0</v>
       </c>
       <c r="L261" t="n">
-        <v>22.4999999999999</v>
+        <v>22.49999999999999</v>
       </c>
       <c r="M261" t="n">
-        <v>2.870879740444849e-13</v>
+        <v>-3.229739708000455e-14</v>
       </c>
       <c r="N261" t="n">
-        <v>69.60600000000011</v>
+        <v>95.59500000000001</v>
       </c>
       <c r="O261" t="n">
-        <v>900.957575757576</v>
+        <v>848.4545454545455</v>
       </c>
       <c r="P261" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q261" t="n">
         <v>47.87888888888889</v>
@@ -17451,7 +17451,7 @@
         <v>21</v>
       </c>
       <c r="D262" t="n">
-        <v>93.696</v>
+        <v>119.884</v>
       </c>
       <c r="E262" t="n">
         <v>44.625</v>
@@ -17475,19 +17475,19 @@
         <v>0</v>
       </c>
       <c r="L262" t="n">
-        <v>7.999999999999996</v>
+        <v>8</v>
       </c>
       <c r="M262" t="n">
-        <v>4.440892098500626e-15</v>
+        <v>0</v>
       </c>
       <c r="N262" t="n">
-        <v>85.85599999999999</v>
+        <v>112.044</v>
       </c>
       <c r="O262" t="n">
-        <v>814.2343434343436</v>
+        <v>735.278787878788</v>
       </c>
       <c r="P262" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q262" t="n">
         <v>49.58333333333333</v>
@@ -17516,7 +17516,7 @@
         <v>22</v>
       </c>
       <c r="D263" t="n">
-        <v>98.786</v>
+        <v>110.043</v>
       </c>
       <c r="E263" t="n">
         <v>40.775</v>
@@ -17540,19 +17540,19 @@
         <v>0</v>
       </c>
       <c r="L263" t="n">
-        <v>29.99999999999963</v>
+        <v>30</v>
       </c>
       <c r="M263" t="n">
-        <v>1.72252784426691e-13</v>
+        <v>3.588599675556063e-15</v>
       </c>
       <c r="N263" t="n">
-        <v>69.38600000000039</v>
+        <v>80.64300000000003</v>
       </c>
       <c r="O263" t="n">
-        <v>744.1474747474747</v>
+        <v>653.8212121212122</v>
       </c>
       <c r="P263" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q263" t="n">
         <v>45.30555555555555</v>
@@ -17581,7 +17581,7 @@
         <v>23</v>
       </c>
       <c r="D264" t="n">
-        <v>98.786</v>
+        <v>110.043</v>
       </c>
       <c r="E264" t="n">
         <v>40.775</v>
@@ -17605,19 +17605,19 @@
         <v>0</v>
       </c>
       <c r="L264" t="n">
-        <v>46.49999999999999</v>
+        <v>46.5</v>
       </c>
       <c r="M264" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>0</v>
       </c>
       <c r="N264" t="n">
-        <v>53.21600000000003</v>
+        <v>64.47300000000003</v>
       </c>
       <c r="O264" t="n">
-        <v>690.3939393939393</v>
+        <v>588.6969696969697</v>
       </c>
       <c r="P264" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q264" t="n">
         <v>45.30555555555555</v>
@@ -17646,7 +17646,7 @@
         <v>24</v>
       </c>
       <c r="D265" t="n">
-        <v>97.666</v>
+        <v>102.145</v>
       </c>
       <c r="E265" t="n">
         <v>34.648</v>
@@ -17676,13 +17676,13 @@
         <v>7.105427357601002e-15</v>
       </c>
       <c r="N265" t="n">
-        <v>62.87600000000001</v>
+        <v>67.35499999999999</v>
       </c>
       <c r="O265" t="n">
-        <v>626.8828282828282</v>
+        <v>520.6616161616162</v>
       </c>
       <c r="P265" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q265" t="n">
         <v>38.49777777777778</v>
@@ -17711,7 +17711,7 @@
         <v>1</v>
       </c>
       <c r="D266" t="n">
-        <v>67.804</v>
+        <v>68.551</v>
       </c>
       <c r="E266" t="n">
         <v>35.363</v>
@@ -17732,10 +17732,10 @@
         <v>0</v>
       </c>
       <c r="K266" t="n">
-        <v>178.399876314162</v>
+        <v>179.1621212121212</v>
       </c>
       <c r="L266" t="n">
-        <v>69.18775510204082</v>
+        <v>69.95</v>
       </c>
       <c r="M266" t="n">
         <v>121.2121212121212</v>
@@ -17776,7 +17776,7 @@
         <v>2</v>
       </c>
       <c r="D267" t="n">
-        <v>67.804</v>
+        <v>68.551</v>
       </c>
       <c r="E267" t="n">
         <v>35.363</v>
@@ -17797,19 +17797,19 @@
         <v>0</v>
       </c>
       <c r="K267" t="n">
-        <v>97.37074663351721</v>
+        <v>98.89515865727989</v>
       </c>
       <c r="L267" t="n">
-        <v>69.18775510204082</v>
+        <v>69.95</v>
       </c>
       <c r="M267" t="n">
-        <v>46.68299153147639</v>
+        <v>47.44515865727989</v>
       </c>
       <c r="N267" t="n">
         <v>3.552713678800501e-15</v>
       </c>
       <c r="O267" t="n">
-        <v>166.2161616161616</v>
+        <v>166.9707070707071</v>
       </c>
       <c r="P267" t="n">
         <v>1</v>
@@ -17841,7 +17841,7 @@
         <v>3</v>
       </c>
       <c r="D268" t="n">
-        <v>67.804</v>
+        <v>68.551</v>
       </c>
       <c r="E268" t="n">
         <v>35.363</v>
@@ -17871,7 +17871,7 @@
         <v>0</v>
       </c>
       <c r="N268" t="n">
-        <v>45.754</v>
+        <v>46.501</v>
       </c>
       <c r="O268" t="n">
         <v>120</v>
@@ -17906,7 +17906,7 @@
         <v>4</v>
       </c>
       <c r="D269" t="n">
-        <v>67.804</v>
+        <v>68.483</v>
       </c>
       <c r="E269" t="n">
         <v>38.078</v>
@@ -17927,19 +17927,19 @@
         <v>0</v>
       </c>
       <c r="K269" t="n">
-        <v>80.87156287675771</v>
+        <v>82.25720646997704</v>
       </c>
       <c r="L269" t="n">
-        <v>69.18775510204081</v>
+        <v>69.88061224489796</v>
       </c>
       <c r="M269" t="n">
-        <v>38.6838077747169</v>
+        <v>39.37659422507907</v>
       </c>
       <c r="N269" t="n">
-        <v>1.06581410364015e-14</v>
+        <v>-3.552713678800501e-15</v>
       </c>
       <c r="O269" t="n">
-        <v>158.2969696969697</v>
+        <v>158.9828282828283</v>
       </c>
       <c r="P269" t="n">
         <v>1</v>
@@ -17971,7 +17971,7 @@
         <v>5</v>
       </c>
       <c r="D270" t="n">
-        <v>67.804</v>
+        <v>68.483</v>
       </c>
       <c r="E270" t="n">
         <v>38.078</v>
@@ -18001,7 +18001,7 @@
         <v>0</v>
       </c>
       <c r="N270" t="n">
-        <v>37.914</v>
+        <v>38.593</v>
       </c>
       <c r="O270" t="n">
         <v>120</v>
@@ -18036,7 +18036,7 @@
         <v>6</v>
       </c>
       <c r="D271" t="n">
-        <v>75.039</v>
+        <v>75.066</v>
       </c>
       <c r="E271" t="n">
         <v>38.078</v>
@@ -18057,19 +18057,19 @@
         <v>0</v>
       </c>
       <c r="K271" t="n">
-        <v>183.9410336096483</v>
+        <v>195.2531474297708</v>
       </c>
       <c r="L271" t="n">
-        <v>76.5704081632653</v>
+        <v>76.59795918367347</v>
       </c>
       <c r="M271" t="n">
-        <v>127.870625446383</v>
+        <v>139.1551882460973</v>
       </c>
       <c r="N271" t="n">
-        <v>1.06581410364015e-14</v>
+        <v>-3.552713678800501e-15</v>
       </c>
       <c r="O271" t="n">
-        <v>246.5919191919192</v>
+        <v>257.7636363636364</v>
       </c>
       <c r="P271" t="n">
         <v>1</v>
@@ -18101,7 +18101,7 @@
         <v>7</v>
       </c>
       <c r="D272" t="n">
-        <v>78.58799999999999</v>
+        <v>84.11799999999999</v>
       </c>
       <c r="E272" t="n">
         <v>48.821</v>
@@ -18131,10 +18131,10 @@
         <v>0</v>
       </c>
       <c r="N272" t="n">
-        <v>61.43799999999999</v>
+        <v>66.96799999999999</v>
       </c>
       <c r="O272" t="n">
-        <v>184.5333333333333</v>
+        <v>190.1191919191919</v>
       </c>
       <c r="P272" t="n">
         <v>0</v>
@@ -18166,7 +18166,7 @@
         <v>8</v>
       </c>
       <c r="D273" t="n">
-        <v>78.58799999999999</v>
+        <v>84.11799999999999</v>
       </c>
       <c r="E273" t="n">
         <v>48.821</v>
@@ -18196,7 +18196,7 @@
         <v>0</v>
       </c>
       <c r="N273" t="n">
-        <v>63.88799999999999</v>
+        <v>69.41799999999999</v>
       </c>
       <c r="O273" t="n">
         <v>120</v>
@@ -18231,7 +18231,7 @@
         <v>9</v>
       </c>
       <c r="D274" t="n">
-        <v>118.618</v>
+        <v>125.853</v>
       </c>
       <c r="E274" t="n">
         <v>61.411</v>
@@ -18252,13 +18252,13 @@
         <v>0</v>
       </c>
       <c r="K274" t="n">
-        <v>112.0590795608111</v>
+        <v>119.4417326220356</v>
       </c>
       <c r="L274" t="n">
-        <v>121.0387755102041</v>
+        <v>128.4214285714285</v>
       </c>
       <c r="M274" t="n">
-        <v>1.020304050607067</v>
+        <v>1.020304050607081</v>
       </c>
       <c r="N274" t="n">
         <v>0</v>
@@ -18296,7 +18296,7 @@
         <v>10</v>
       </c>
       <c r="D275" t="n">
-        <v>116.928</v>
+        <v>138.408</v>
       </c>
       <c r="E275" t="n">
         <v>45.383</v>
@@ -18317,13 +18317,13 @@
         <v>-0</v>
       </c>
       <c r="K275" t="n">
-        <v>115.2938775510204</v>
+        <v>137.2122448979592</v>
       </c>
       <c r="L275" t="n">
-        <v>118.2938775510204</v>
+        <v>140.2122448979592</v>
       </c>
       <c r="M275" t="n">
-        <v>-7.177199351112124e-15</v>
+        <v>-2.153159805333638e-14</v>
       </c>
       <c r="N275" t="n">
         <v>0.9999999999999787</v>
@@ -18361,7 +18361,7 @@
         <v>11</v>
       </c>
       <c r="D276" t="n">
-        <v>116.928</v>
+        <v>138.408</v>
       </c>
       <c r="E276" t="n">
         <v>45.383</v>
@@ -18379,22 +18379,22 @@
         <v>0</v>
       </c>
       <c r="J276" t="n">
-        <v>275.144090669632</v>
+        <v>281.1437845784168</v>
       </c>
       <c r="K276" t="n">
         <v>0</v>
       </c>
       <c r="L276" t="n">
-        <v>119.3142857142857</v>
+        <v>141.2326530612245</v>
       </c>
       <c r="M276" t="n">
-        <v>156.8298049553462</v>
+        <v>140.9111315171922</v>
       </c>
       <c r="N276" t="n">
         <v>7.105427357601002e-15</v>
       </c>
       <c r="O276" t="n">
-        <v>275.2615069057927</v>
+        <v>259.5020202020203</v>
       </c>
       <c r="P276" t="n">
         <v>1</v>
@@ -18426,7 +18426,7 @@
         <v>12</v>
       </c>
       <c r="D277" t="n">
-        <v>115.137</v>
+        <v>139.087</v>
       </c>
       <c r="E277" t="n">
         <v>49.5</v>
@@ -18450,16 +18450,16 @@
         <v>0</v>
       </c>
       <c r="L277" t="n">
-        <v>0.9999999999999789</v>
+        <v>0.9999999999999439</v>
       </c>
       <c r="M277" t="n">
-        <v>-7.962205530140012e-15</v>
+        <v>-1.682156097916901e-15</v>
       </c>
       <c r="N277" t="n">
-        <v>114.157</v>
+        <v>138.1070000000001</v>
       </c>
       <c r="O277" t="n">
-        <v>159.9514058956917</v>
+        <v>120</v>
       </c>
       <c r="P277" t="n">
         <v>0</v>
@@ -18491,7 +18491,7 @@
         <v>13</v>
       </c>
       <c r="D278" t="n">
-        <v>112.44</v>
+        <v>136.236</v>
       </c>
       <c r="E278" t="n">
         <v>56.911</v>
@@ -18509,22 +18509,22 @@
         <v>0</v>
       </c>
       <c r="J278" t="n">
-        <v>142.4457122242837</v>
+        <v>139.5365285508143</v>
       </c>
       <c r="K278" t="n">
         <v>0</v>
       </c>
       <c r="L278" t="n">
-        <v>114.734693877551</v>
+        <v>139.0163265306122</v>
       </c>
       <c r="M278" t="n">
-        <v>29.21101834673267</v>
+        <v>2.020202020202006</v>
       </c>
       <c r="N278" t="n">
         <v>0</v>
       </c>
       <c r="O278" t="n">
-        <v>188.870314058957</v>
+        <v>122</v>
       </c>
       <c r="P278" t="n">
         <v>1</v>
@@ -18556,7 +18556,7 @@
         <v>14</v>
       </c>
       <c r="D279" t="n">
-        <v>112.44</v>
+        <v>136.236</v>
       </c>
       <c r="E279" t="n">
         <v>56.911</v>
@@ -18580,16 +18580,16 @@
         <v>0</v>
       </c>
       <c r="L279" t="n">
-        <v>114.734693877551</v>
+        <v>139.0163265306122</v>
       </c>
       <c r="M279" t="n">
-        <v>25.7612244897959</v>
+        <v>1.479591836734676</v>
       </c>
       <c r="N279" t="n">
         <v>0</v>
       </c>
       <c r="O279" t="n">
-        <v>214.3739263038549</v>
+        <v>123.4647959183673</v>
       </c>
       <c r="P279" t="n">
         <v>1</v>
@@ -18621,7 +18621,7 @@
         <v>15</v>
       </c>
       <c r="D280" t="n">
-        <v>114.258</v>
+        <v>122.799</v>
       </c>
       <c r="E280" t="n">
         <v>53.581</v>
@@ -18639,22 +18639,22 @@
         <v>0</v>
       </c>
       <c r="J280" t="n">
-        <v>124.284693877551</v>
+        <v>253.9616718512663</v>
       </c>
       <c r="K280" t="n">
         <v>0</v>
       </c>
       <c r="L280" t="n">
-        <v>116.5897959183673</v>
+        <v>125.3051020408163</v>
       </c>
       <c r="M280" t="n">
-        <v>20.69489795918367</v>
+        <v>141.6565698104498</v>
       </c>
       <c r="N280" t="n">
         <v>0</v>
       </c>
       <c r="O280" t="n">
-        <v>234.8618752834468</v>
+        <v>263.7048000307126</v>
       </c>
       <c r="P280" t="n">
         <v>1</v>
@@ -18686,7 +18686,7 @@
         <v>16</v>
       </c>
       <c r="D281" t="n">
-        <v>131.363</v>
+        <v>140.444</v>
       </c>
       <c r="E281" t="n">
         <v>41.57</v>
@@ -18704,22 +18704,22 @@
         <v>0</v>
       </c>
       <c r="J281" t="n">
-        <v>698.3102040816327</v>
+        <v>703.3102040816327</v>
       </c>
       <c r="K281" t="n">
         <v>0</v>
       </c>
       <c r="L281" t="n">
-        <v>134.0438775510204</v>
+        <v>143.3102040816326</v>
       </c>
       <c r="M281" t="n">
-        <v>577.7663265306124</v>
+        <v>573.5000000000001</v>
       </c>
       <c r="N281" t="n">
-        <v>2.131628207280301e-14</v>
+        <v>-7.105427357601002e-15</v>
       </c>
       <c r="O281" t="n">
-        <v>806.8505385487531</v>
+        <v>831.4698000307127</v>
       </c>
       <c r="P281" t="n">
         <v>1</v>
@@ -18751,7 +18751,7 @@
         <v>17</v>
       </c>
       <c r="D282" t="n">
-        <v>131.363</v>
+        <v>140.444</v>
       </c>
       <c r="E282" t="n">
         <v>41.57</v>
@@ -18769,25 +18769,25 @@
         <v>0</v>
       </c>
       <c r="J282" t="n">
-        <v>90.3001036026656</v>
+        <v>103.7897959183673</v>
       </c>
       <c r="K282" t="n">
         <v>0</v>
       </c>
       <c r="L282" t="n">
-        <v>99.30010360266569</v>
+        <v>112.7897959183672</v>
       </c>
       <c r="M282" t="n">
-        <v>7.177199351112124e-15</v>
+        <v>2.153159805333637e-14</v>
       </c>
       <c r="N282" t="n">
-        <v>34.04889846938762</v>
+        <v>29.91000000000016</v>
       </c>
       <c r="O282" t="n">
-        <v>772.4577118119979</v>
+        <v>801.2576788185913</v>
       </c>
       <c r="P282" t="n">
-        <v>1.657933050106901e-16</v>
+        <v>0</v>
       </c>
       <c r="Q282" t="n">
         <v>46.18888888888889</v>
@@ -18816,7 +18816,7 @@
         <v>18</v>
       </c>
       <c r="D283" t="n">
-        <v>94.574</v>
+        <v>122.803</v>
       </c>
       <c r="E283" t="n">
         <v>48.767</v>
@@ -18834,25 +18834,25 @@
         <v>0</v>
       </c>
       <c r="J283" t="n">
-        <v>68.80918367346938</v>
+        <v>83.82948772407644</v>
       </c>
       <c r="K283" t="n">
         <v>0</v>
       </c>
       <c r="L283" t="n">
-        <v>73.80918367346948</v>
+        <v>88.82948772407634</v>
       </c>
       <c r="M283" t="n">
-        <v>-1.866071831289152e-13</v>
+        <v>0</v>
       </c>
       <c r="N283" t="n">
-        <v>22.24099999999992</v>
+        <v>35.75010203040518</v>
       </c>
       <c r="O283" t="n">
-        <v>749.9920552463412</v>
+        <v>765.1464646464649</v>
       </c>
       <c r="P283" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q283" t="n">
         <v>54.18555555555556</v>
@@ -18881,7 +18881,7 @@
         <v>19</v>
       </c>
       <c r="D284" t="n">
-        <v>91.65600000000001</v>
+        <v>117.645</v>
       </c>
       <c r="E284" t="n">
         <v>43.091</v>
@@ -18905,16 +18905,16 @@
         <v>0</v>
       </c>
       <c r="L284" t="n">
-        <v>3.500000000000001</v>
+        <v>3.500000000000095</v>
       </c>
       <c r="M284" t="n">
-        <v>-6.683766895723165e-14</v>
+        <v>-4.575464586333979e-14</v>
       </c>
       <c r="N284" t="n">
-        <v>88.22600000000001</v>
+        <v>114.2149999999999</v>
       </c>
       <c r="O284" t="n">
-        <v>660.8748835291694</v>
+        <v>649.7777777777781</v>
       </c>
       <c r="P284" t="n">
         <v>0</v>
@@ -18946,7 +18946,7 @@
         <v>20</v>
       </c>
       <c r="D285" t="n">
-        <v>91.65600000000001</v>
+        <v>117.645</v>
       </c>
       <c r="E285" t="n">
         <v>43.091</v>
@@ -18970,16 +18970,16 @@
         <v>0</v>
       </c>
       <c r="L285" t="n">
-        <v>3.999999999999996</v>
+        <v>3.999999999999868</v>
       </c>
       <c r="M285" t="n">
-        <v>-1.928872325611383e-14</v>
+        <v>-5.831474472778602e-15</v>
       </c>
       <c r="N285" t="n">
-        <v>87.73600000000002</v>
+        <v>113.7250000000001</v>
       </c>
       <c r="O285" t="n">
-        <v>572.2526613069472</v>
+        <v>534.9040404040405</v>
       </c>
       <c r="P285" t="n">
         <v>0</v>
@@ -19011,7 +19011,7 @@
         <v>21</v>
       </c>
       <c r="D286" t="n">
-        <v>93.696</v>
+        <v>119.884</v>
       </c>
       <c r="E286" t="n">
         <v>44.625</v>
@@ -19038,16 +19038,16 @@
         <v>3</v>
       </c>
       <c r="M286" t="n">
-        <v>-4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="N286" t="n">
-        <v>90.75599999999999</v>
+        <v>116.944</v>
       </c>
       <c r="O286" t="n">
-        <v>480.5799340342199</v>
+        <v>416.778787878788</v>
       </c>
       <c r="P286" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q286" t="n">
         <v>49.58333333333333</v>
@@ -19076,7 +19076,7 @@
         <v>22</v>
       </c>
       <c r="D287" t="n">
-        <v>98.786</v>
+        <v>110.043</v>
       </c>
       <c r="E287" t="n">
         <v>40.775</v>
@@ -19100,16 +19100,16 @@
         <v>0</v>
       </c>
       <c r="L287" t="n">
-        <v>4.000000000000004</v>
+        <v>4</v>
       </c>
       <c r="M287" t="n">
-        <v>-3.552713678800501e-15</v>
+        <v>0</v>
       </c>
       <c r="N287" t="n">
-        <v>94.86600000000001</v>
+        <v>106.123</v>
       </c>
       <c r="O287" t="n">
-        <v>384.7556916099774</v>
+        <v>309.5838383838384</v>
       </c>
       <c r="P287" t="n">
         <v>0</v>
@@ -19141,7 +19141,7 @@
         <v>23</v>
       </c>
       <c r="D288" t="n">
-        <v>98.786</v>
+        <v>110.043</v>
       </c>
       <c r="E288" t="n">
         <v>40.775</v>
@@ -19165,16 +19165,16 @@
         <v>0</v>
       </c>
       <c r="L288" t="n">
-        <v>9.999999999999996</v>
+        <v>10</v>
       </c>
       <c r="M288" t="n">
-        <v>3.552713678800501e-15</v>
+        <v>0</v>
       </c>
       <c r="N288" t="n">
-        <v>88.98600000000002</v>
+        <v>100.243</v>
       </c>
       <c r="O288" t="n">
-        <v>294.8708431251289</v>
+        <v>208.3282828282829</v>
       </c>
       <c r="P288" t="n">
         <v>0</v>
@@ -19206,7 +19206,7 @@
         <v>24</v>
       </c>
       <c r="D289" t="n">
-        <v>97.666</v>
+        <v>102.145</v>
       </c>
       <c r="E289" t="n">
         <v>34.648</v>
@@ -19233,13 +19233,13 @@
         <v>15</v>
       </c>
       <c r="M289" t="n">
-        <v>3.552713678800501e-15</v>
+        <v>0</v>
       </c>
       <c r="N289" t="n">
-        <v>82.96600000000001</v>
+        <v>87.44499999999999</v>
       </c>
       <c r="O289" t="n">
-        <v>211.0668027210885</v>
+        <v>120</v>
       </c>
       <c r="P289" t="n">
         <v>0</v>
@@ -19476,7 +19476,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>275.144090669632</v>
+        <v>281.1437845784168</v>
       </c>
       <c r="C12" t="n">
         <v>50.42555555555555</v>
@@ -19510,7 +19510,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>142.4457122242837</v>
+        <v>139.5365285508143</v>
       </c>
       <c r="C14" t="n">
         <v>63.23444444444444</v>
@@ -19544,7 +19544,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>124.284693877551</v>
+        <v>253.9616718512663</v>
       </c>
       <c r="C16" t="n">
         <v>59.53444444444445</v>
@@ -19561,7 +19561,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>698.3102040816327</v>
+        <v>703.3102040816327</v>
       </c>
       <c r="C17" t="n">
         <v>46.18888888888889</v>
@@ -19578,7 +19578,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>90.3001036026656</v>
+        <v>103.7897959183673</v>
       </c>
       <c r="C18" t="n">
         <v>46.18888888888889</v>
@@ -19595,7 +19595,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>68.80918367346938</v>
+        <v>83.82948772407644</v>
       </c>
       <c r="C19" t="n">
         <v>54.18555555555556</v>
